--- a/datesheet.xlsx
+++ b/datesheet.xlsx
@@ -1,27 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878A16EB-EE59-47AC-BCD5-6E0F27FC9332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" tabRatio="375" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FSC" sheetId="16" r:id="rId1"/>
-    <sheet name="FSM" sheetId="13" r:id="rId2"/>
-    <sheet name="EE" sheetId="15" r:id="rId3"/>
+    <sheet name="FSC" sheetId="16" state="hidden" r:id="rId1"/>
+    <sheet name="FSC Final" sheetId="17" r:id="rId2"/>
+    <sheet name="FSM Final" sheetId="18" r:id="rId3"/>
+    <sheet name="FSM" sheetId="13" state="hidden" r:id="rId4"/>
+    <sheet name="FSE Final" sheetId="19" r:id="rId5"/>
+    <sheet name="EE" sheetId="15" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">EE!$A$1:$L$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">FSM!$A$1:$N$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">EE!$A$1:$L$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'FSE Final'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">FSM!$A$1:$P$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'FSM Final'!$A$1:$F$95</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="402">
   <si>
     <t>Days &amp; Date</t>
   </si>
@@ -1247,6 +1251,24 @@
   </si>
   <si>
     <t>5:20 to 6:20 PM</t>
+  </si>
+  <si>
+    <t>Jumma Prayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 to 13 April 2026    (FAST-School of Computing)        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sessional-2  Exams Schedule  Spring - 2026                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 to 13 April 2026                      FAST-School of Management               </t>
+  </si>
+  <si>
+    <t>09 to 13 April 2026                                       FAST-School of Engineering</t>
+  </si>
+  <si>
+    <t>Sessional-2 Exams Schedule  Spring - 2026</t>
   </si>
   <si>
     <t>MG3033-Principles of Leadership
@@ -1335,6 +1357,10 @@
  Batch Spring 2026</t>
   </si>
   <si>
+    <t>Final
+Issued: 03-April-26</t>
+  </si>
+  <si>
     <t>EE 6005 Application of Deep Learning in Engineering PEE-1A</t>
   </si>
   <si>
@@ -1453,34 +1479,697 @@
     <t>Detail seating plan will be shared separately on daily basis during examination and students should follow that seating plan accordingly</t>
   </si>
   <si>
-    <t>Final-Revised
-Issued: 08-April-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 to 16 April 2026    (FAST-School of Computing)        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 to 16 April 2026                     FAST-School of Management               </t>
-  </si>
-  <si>
-    <t>13 to 16 April 2026                                    FAST-School of Engineering</t>
-  </si>
-  <si>
-    <t>Revised Sessional-2 Exams Schedule  Spring - 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revised Sessional-2  Exams Schedule  Spring - 2026                     </t>
+    <t>SE2002 Software Design and Architecture
+BS(SE) (A)
+2022</t>
+  </si>
+  <si>
+    <t>9:00 to 12:00 PM</t>
+  </si>
+  <si>
+    <t>1:00 to 4:00 PM</t>
+  </si>
+  <si>
+    <t>5:00 to 8:00 PM</t>
+  </si>
+  <si>
+    <t>Schedule of Final Examination of Spring Semester 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       FAST-School of Management</t>
+  </si>
+  <si>
+    <t>18 May to 12 June 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       FAST-School of Engineering                       </t>
+  </si>
+  <si>
+    <t>MG6003 Research and Theory in Management
+PMG-2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MG6016-Seminars in Management PMG-3A
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AF6001-Contemporary Trends in Finance PMG-1A  </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SS1006 English – II
+ BS(AF)-2A,B
+BBA-2A,B,C,D
+BS(FT)-2A,B,C,D
+BS(BA)-2A,B,C
+2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AF4013-Artificial Intelligence in Business Decision
+2022
+BFT-8A, 8B
+</t>
+  </si>
+  <si>
+    <t>MG6004 Advanced Qualitative Research Methods
+PMG-2A</t>
+  </si>
+  <si>
+    <t>MG6002 Advanced Quantitative Research Methods
+PMG-2A</t>
+  </si>
+  <si>
+    <t>AL2002 Artificial Intelligence - Lab
+BS(CY) (A,B)
+2023</t>
+  </si>
+  <si>
+    <t>AL4002Computer Vision - Lab
+BS(AI) (A,B)
+2023</t>
+  </si>
+  <si>
+    <t>AL4002Computer Vision - Lab
+BS(AI) (A)
+2022</t>
+  </si>
+  <si>
+    <t>CL1002  Programming Fundamentals - Lab
+BS(CS) (A,B,C)
+ BS(SE) (A) 
+BS(AI) (A, M)
+BS(CY) (A)
+2025</t>
+  </si>
+  <si>
+    <t>CL2001  Data Structures - Lab        
+ BS(CS) (A,B)      
+BS(SE) (A) 
+BS(CYS) (A)
+BS(AI) (A,B)
+2024 ( R )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL2006 Operating Systems - Lab             
+BS(CS) (A,B,C,D,E,F,G)
+BS(AI) (A,B,C) 
+BS(SE) (A,B,C) 
+BS(DS) (A,B) 
+2024     </t>
+  </si>
+  <si>
+    <t>CL3001 Computer Networks - Lab
+ BS(AI)-(A,B)
+BS(SE)-(A,B)
+2023</t>
+  </si>
+  <si>
+    <t>CL3001 Computer Networks - Lab
+ BS(CY)-(A,B) 
+2024</t>
+  </si>
+  <si>
+    <t>DL2004 Fundamental of Big Data Analytics - Lab
+ BS(DS) (A)
+2022</t>
+  </si>
+  <si>
+    <t>DL3002 Data Mining - Lab
+BS(DS) (B)
+2022</t>
+  </si>
+  <si>
+    <t>EL2003 Computer Organization and Assembly Language - Lab
+BS(CY)-A,B
+BS(SE)-A,B,C
+2024</t>
+  </si>
+  <si>
+    <t>SL1008 Communication and Presentation Skills - Lab
+BCS-9A</t>
+  </si>
+  <si>
+    <t>SL1014  Expository Writing - Lab
+  BS(CS) (2A1,2A2,2B1,2B2,2C1,2C2,2D1,2D2,2E1,2E2,2F1,2F2,2G1,2G2,2H1,2H2,2J1,2J2)
+BS(SE) 2A1,2A2,2B1,2B2,2C1,2C2,2D1,2D2)
+BS(AI) (2A1,2A2,2B1,2B2,2C1,2C2)
+BS(DS) (2A1,2A2,2B1,2B2)
+BS(CY) (2A1,2A2,2B1,2B2,2C1,2C2)
+2025</t>
+  </si>
+  <si>
+    <t>SL2002 Software Design and Architecture - Lab
+BS(SE) (A)
+2022</t>
+  </si>
+  <si>
+    <t>SL3003 Web Engineering - Lab
+ BS(SE) (A)
+2022</t>
+  </si>
+  <si>
+    <t>YL2002 Digital Forensics - Lab
+BS(CY)-A,B
+ 2022</t>
+  </si>
+  <si>
+    <t>YL3006 Digital Forensics - Lab
+BS(CY)-A,B
+ 2023</t>
+  </si>
+  <si>
+    <t>YL3002 Vulnerability Assessment and Reverse Engg - Lab
+BCY- (A)
+2022</t>
+  </si>
+  <si>
+    <t>YL4001 Secure Software Design - Lab
+BS(CY)-A,B
+ 2023</t>
+  </si>
+  <si>
+    <t>CL1002-Programming Fundamentals - Lab 
+BS(CE) -ABC
+2025</t>
+  </si>
+  <si>
+    <t>CL1011 Programming for Engineers - Lab
+BS(EE) -ABCD (2025)</t>
+  </si>
+  <si>
+    <t>CL2002 Data Structures and Algorithms - Lab
+BCE-4AB
+2024</t>
+  </si>
+  <si>
+    <t>CL2018 Operating Systems - Lab
+BEE-6A,B
+2023</t>
+  </si>
+  <si>
+    <t>CL2021 Object Oriented Data Structures - Lab
+BEE-4A
+2024</t>
+  </si>
+  <si>
+    <t>EL1005 Digital Logic Design - Lab
+BCE-4AB
+BEE-4ABC
+(2024)</t>
+  </si>
+  <si>
+    <t>EL1006 Engineering Workshop - Lab
+BCE-ABC
+BEE-ABCD
+2025</t>
+  </si>
+  <si>
+    <t>EL2004 Electrical Network Analysis - Lab
+BEE-4A,B
+2024</t>
+  </si>
+  <si>
+    <t>EL2008 Signals and Systems - Lab
+BCE-4AB
+BEE-4ABC
+2024</t>
+  </si>
+  <si>
+    <t>EL2015 Electro-Mechanical Systems - Lab
+BEE-4ABC
+BEE-6ABCD
+2024</t>
+  </si>
+  <si>
+    <t>EL3003 Analogue and Digital Communication - Lab
+BEE-6A
+2023</t>
+  </si>
+  <si>
+    <t>EL3004 Feedback Control System - Lab
+BEE-6A,B
+2023</t>
+  </si>
+  <si>
+    <t>EL3031 Digital Signal Processing - Lab 
+BEE-6A
+2023</t>
+  </si>
+  <si>
+    <t>EL3032 Power Electronics - Lab
+BEE-6A
+2023</t>
+  </si>
+  <si>
+    <t>EL3034 VLSI - Lab
+BEE-8A
+2022</t>
+  </si>
+  <si>
+    <t>EL4031 Computer Architecture - Lab
+BEE-6A,B
+2023</t>
+  </si>
+  <si>
+    <t>EL4033 Industrial Processes Control - Lab 
+BEE-8A
+2022</t>
+  </si>
+  <si>
+    <t>IL3031 Introduction to Internet of Things - Lab
+BEE-8AB
+2022</t>
+  </si>
+  <si>
+    <t>BL3001 Machine Learning for Business Analytics - Lab
+2023
+BS(BA)-6A,B</t>
+  </si>
+  <si>
+    <t>BL3005 Database Systems for Business - Lab
+2023
+BS(BA)-6A,B
+BS(BA)-8A</t>
+  </si>
+  <si>
+    <t>BL5004 Machine Learning Models for Business Analytics - Lab
+MSBA-2A</t>
+  </si>
+  <si>
+    <t>CL1001 IT in Business - Lab
+2025
+BBA-2A,B,C,D</t>
+  </si>
+  <si>
+    <t>CL2013 Introduction to Database Systems - Lab
+2024
+BS(FT)-4A,B,C,D</t>
+  </si>
+  <si>
+    <t>CL2016 Programming for Business - Lab
+2025
+BS(FT)-2A,B,C,D</t>
+  </si>
+  <si>
+    <t>CL3010 Web Programming - Lab
+2023
+BS(FT)-6A,B</t>
+  </si>
+  <si>
+    <t>FL3001 Financial Management - Lab
+2024
+BS(FT)-4A,B,C,D</t>
+  </si>
+  <si>
+    <t>FL3007 Financial Data Analytics - Lab
+2022
+BS(FT)-8A</t>
+  </si>
+  <si>
+    <t>FL 3008 Business Research and Data Mining - Lab
+2023
+BS(FT)-6A,B</t>
+  </si>
+  <si>
+    <t>LG2009 Data Analysis for Business II - Lab
+2024
+BS(FT)-4A,B,C,D</t>
+  </si>
+  <si>
+    <t>ML3010 Methods in Business Research - Lab
+2023
+BS(AF)-6A,B
+BBA-6A,B
+BS(BA)-6A,B</t>
+  </si>
+  <si>
+    <t>CL1004 Object Oriented Programming - Lab   
+BS(AI) (A,B, C)
+BS(DS) (A,B)
+2025</t>
+  </si>
+  <si>
+    <t>CL1004 Object Oriented Programming - Lab   
+BS(CY) (A,B,C)
+2025</t>
+  </si>
+  <si>
+    <t>CL1004 Object Oriented Programming - Lab   
+ BS(CS) (A,B,C,D,E,F, G,H, J)      
+2025</t>
+  </si>
+  <si>
+    <t>CL1004 Object Oriented Programming - Lab   
+    BS(SE) (A,B,C,D) 
+2025</t>
+  </si>
+  <si>
+    <t>AL2002 Artificial Intelligence - Lab
+BS(SE) (A,B)
+2023</t>
+  </si>
+  <si>
+    <t>EL1005 Digital Logic Design - Lab 
+BS(AI) (A,B, C)
+BS(DS) (A,B)
+2025</t>
+  </si>
+  <si>
+    <t>EL1005 Digital Logic Design - Lab  
+BS(CY) (A,B,C)
+2025</t>
+  </si>
+  <si>
+    <t>EL1005 Digital Logic Design - Lab  
+  BS(SE) (A,B,C,D) 
+2025</t>
+  </si>
+  <si>
+    <t>AL2002 Artificial Intelligence - Lab 
+BS(AI) (A,B,C)
+BS(DS) (A,B,C)
+  2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL2005 Database Systems - Lab            
+BS(AI) (A,B,C) 
+BS(DS) (A,B) 
+2024      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL2005 Database Systems - Lab            
+BS(CS) (A,B,C,D,E,F,G)
+2024      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL2005 Database Systems - Lab            
+BS(SE) (A,B,C) 
+2024      </t>
+  </si>
+  <si>
+    <t>CS4061 Ethical Hacking Concepts and Practices 
+BS(CY)-A,B
+2023</t>
+  </si>
+  <si>
+    <t>AL2002 Artificial Intelligence - Lab
+ BS(CS) (A,B,C,D,E,F,G) 
+  2024</t>
+  </si>
+  <si>
+    <t>AL2002 Artificial Intelligence - Lab
+BS(DS) (A,B,C)
+2023</t>
+  </si>
+  <si>
+    <t>SS1014  Expository Writing
+  BS(CS) (A,B,C,D,E,F, G,H, J) 
+BS(SE) (A,B,C,D) 
+BS(AI) (A,B, C)
+BS(DS) (A,B)
+BS(CY) (A,B,C)
+2025</t>
+  </si>
+  <si>
+    <t>AL2002 Artificial Intelligence - Lab
+ BS(CS) (A,B,C,D,E,F,G) 
+2023</t>
+  </si>
+  <si>
+    <t>CS6025Advanced Machine LearningPCS-2A</t>
+  </si>
+  <si>
+    <t>CS6058Advanced Topic in Agentic AIPCS-2A</t>
+  </si>
+  <si>
+    <t>CS6001Advanced Topics in CS PCS-2A</t>
+  </si>
+  <si>
+    <t>CS6027Applied Image ProcessingPCS-2A</t>
+  </si>
+  <si>
+    <t>CS6006Cyber and Network SecurityPCS-2A</t>
+  </si>
+  <si>
+    <t>CS6011Data Analysis and VisualizationPCS-2A</t>
+  </si>
+  <si>
+    <t>CS6018Recent Advances in Deep LearningPCS-2A</t>
+  </si>
+  <si>
+    <t>SE6006Research MethodologyPCS-2A</t>
+  </si>
+  <si>
+    <t>CS6016Research Topics in Cloud ComputingPCS-2A</t>
+  </si>
+  <si>
+    <t>SE6031Research Topics in Software EngineeringPCS-2A</t>
+  </si>
+  <si>
+    <t>SE6007Search-based Software EngineeringPSE-2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FL1002 Financial Accounting - Lab
+2025
+BS(AF)-2A,B
+BBA-2A,B,C,D
+</t>
+  </si>
+  <si>
+    <t>FL1002 Financial Accounting - Lab
+2025
+BS(FT)-2A,B,C,D
+BS(BA)-2A,B,C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL1006 English – II Lab
+ BS(AF)-2A1,2A2,2B1,2B2
+BBA-2A1,2A2,2B1,2B2,2C1,2C2,2D1,2D2
+2025 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL1006 English – II Lab
+BS(FT)-2A1,2A2,2B1,2B2,2C1,2C2,2D1,2D2
+BS(BA)-2A1,2A2,2B1,2B2,2C1,2C2
+2025 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AF1001 Fundamentals of Accounting
+2025
+BBA-2A
+</t>
+  </si>
+  <si>
+    <t>SE6001Advanced Topics in Requirements Engineering PSE-2A</t>
+  </si>
+  <si>
+    <t>CS6033Statistical and Mathematical Methods for DSP CS-2A</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note: All the students are informed please view the above schedule carefully and if anybody has any query/clash, he/she may submit the request on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>link https://forms.gle/dM9mzHJ7Hrjhrogw7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">  by 08-05-2026 afternoon</t>
+    </r>
+  </si>
+  <si>
+    <t>On Friday these exams  will start from 2:00 PM To 5:00 PM</t>
+  </si>
+  <si>
+    <t>MG3033-Principles of Leadership
+2022
+BBA-6A
+BAF-8A</t>
+  </si>
+  <si>
+    <t>MT2001 Statistical Inference 
+BAF-9A</t>
+  </si>
+  <si>
+    <t>BL3004-Database Systems for Business Lab
+3004
+BS(BA)-8A</t>
+  </si>
+  <si>
+    <t>EL2010 Electro-Mechanical Systems Lab
+BEE-6A,B
+2023</t>
+  </si>
+  <si>
+    <t>EL1001 Linear Circuit Analysis - Lab
+BS(CE) -ABC
+BS(EE) -ABCD
+ (2025)</t>
+  </si>
+  <si>
+    <t>SS1021-Understanding of Holy Quran I
+BS(CE) -AB
+ (2025)</t>
+  </si>
+  <si>
+    <t>CS6053 - Research MethodologyPEE-1A</t>
+  </si>
+  <si>
+    <t>EE5004 - SoC Packaging and Signal IntegrityMEE-2A</t>
+  </si>
+  <si>
+    <t>EE5011 - Research MethodologyMEE-1A</t>
+  </si>
+  <si>
+    <t>EE6001 - Reinforcement Learning for EngineersPEE-1A</t>
+  </si>
+  <si>
+    <t>EE6005 - Applications of Deep Learning in EngineeringPEE-1A</t>
+  </si>
+  <si>
+    <t>EE6014 - Biosystems Modeling and SimulationPEE-1A</t>
+  </si>
+  <si>
+    <t>EE5005 - Mixed Signal Integrated Circuit Design MEE-2A</t>
+  </si>
+  <si>
+    <t>EE5006 - Deep Learning MEE-1A</t>
+  </si>
+  <si>
+    <t>EE5048 - VLSI Design Verification and Test MEE-2A</t>
+  </si>
+  <si>
+    <t>NL1007 Applied Physics - Lab
+BEE-2AB
+(2025)</t>
+  </si>
+  <si>
+    <t>CL1009 Applications of Information Communication Technologies - Lab
+BS(EE), 2A
+ (2025)</t>
+  </si>
+  <si>
+    <t>Draft
+Issued:  07-May-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 May to 13 June 2026    (FAST-School of Computing)        </t>
+  </si>
+  <si>
+    <t>18 May to 13 June 2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note: All the students are informed please view the above schedule carefully and if anybody has any query/clash, he/she may submit the request on the link </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://forms.gle/dM9mzHJ7Hrjhrogw7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  by 08-05-2026 afternoon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note: All the students are informed please view the above schedule carefully and if anybody has any query/clash, he/she may submit the request on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>link https://forms.gle/dM9mzHJ7Hrjhrogw7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  by 08-05-2026 afternoon</t>
+    </r>
+  </si>
+  <si>
+    <t>SE5006 Model Bases Testing MSE-1A</t>
+  </si>
+  <si>
+    <t>BA2006 Fundamentals of Business Analytics
+2024
+BS(BA)-4A,B,C</t>
+  </si>
+  <si>
+    <t>SS1021MP  Understanding of Holy Quran I
+PCS-1A, PCS-2A, MAI-2A, MDS-2A</t>
+  </si>
+  <si>
+    <t>SS1022  Understanding of Holy Quran II
+PCS-1A, PCS-2A, MAI-2A, MDS-2A</t>
+  </si>
+  <si>
+    <t>SS1022 Understanding of Holy Quran II 
+ PMG-1A, PMG-2A, MSBA-2A</t>
+  </si>
+  <si>
+    <t>SS1021 Understanding of Holy Quran I 
+PMG-1A, PMG-2A, MSBA-2A</t>
+  </si>
+  <si>
+    <t>SS1021 Understanding of Holy Quran I
+ PEE-1A, MEE-1A</t>
+  </si>
+  <si>
+    <t>SS1022 Understanding of Holy Quran II 
+PEE-1A, MEE-1A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1665,8 +2354,98 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="25"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="25"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="20"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1823,8 +2602,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -2074,12 +2859,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="282">
+  <cellXfs count="400">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2654,26 +3465,321 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="45" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="45" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="45" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -2684,118 +3790,161 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2807,72 +3956,93 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2882,27 +4052,15 @@
     <xf numFmtId="0" fontId="15" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2913,17 +4071,90 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="86">
+  <dxfs count="93">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3852,9 +5083,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3892,9 +5123,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3929,7 +5160,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3964,7 +5195,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4137,7 +5368,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2542061-F1D4-4AC4-AF9C-C98EC8432B54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P47"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4161,59 +5392,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="25" customFormat="1" ht="30.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="315" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="199"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="315"/>
+      <c r="G1" s="315"/>
+      <c r="H1" s="315"/>
+      <c r="I1" s="315"/>
+      <c r="J1" s="315"/>
+      <c r="K1" s="315"/>
+      <c r="L1" s="315"/>
+      <c r="M1" s="315"/>
+      <c r="N1" s="315"/>
     </row>
     <row r="2" spans="1:16" s="25" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="199" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" s="199"/>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="199"/>
-      <c r="F2" s="199"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="199"/>
-      <c r="J2" s="199"/>
-      <c r="K2" s="199"/>
-      <c r="L2" s="199"/>
-      <c r="M2" s="199"/>
+      <c r="A2" s="315" t="s">
+        <v>245</v>
+      </c>
+      <c r="B2" s="315"/>
+      <c r="C2" s="315"/>
+      <c r="D2" s="315"/>
+      <c r="E2" s="315"/>
+      <c r="F2" s="315"/>
+      <c r="G2" s="315"/>
+      <c r="H2" s="315"/>
+      <c r="I2" s="315"/>
+      <c r="J2" s="315"/>
+      <c r="K2" s="315"/>
+      <c r="L2" s="315"/>
+      <c r="M2" s="315"/>
       <c r="N2" s="86"/>
     </row>
     <row r="3" spans="1:16" s="25" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="200" t="s">
-        <v>265</v>
-      </c>
-      <c r="B3" s="200"/>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
-      <c r="L3" s="200"/>
-      <c r="M3" s="200"/>
+      <c r="A3" s="316" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" s="316"/>
+      <c r="C3" s="316"/>
+      <c r="D3" s="316"/>
+      <c r="E3" s="316"/>
+      <c r="F3" s="316"/>
+      <c r="G3" s="316"/>
+      <c r="H3" s="316"/>
+      <c r="I3" s="316"/>
+      <c r="J3" s="316"/>
+      <c r="K3" s="316"/>
+      <c r="L3" s="316"/>
+      <c r="M3" s="316"/>
       <c r="P3" s="46" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="60.75" x14ac:dyDescent="0.2">
@@ -4249,37 +5480,37 @@
       </c>
       <c r="O4" s="144"/>
       <c r="P4" s="53" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="10" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="201">
-        <v>46125</v>
-      </c>
-      <c r="B5" s="204" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="10" customFormat="1" ht="63" x14ac:dyDescent="0.2">
+      <c r="A5" s="303">
+        <v>46121</v>
+      </c>
+      <c r="B5" s="292" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="207"/>
-      <c r="D5" s="197" t="s">
+      <c r="C5" s="275"/>
+      <c r="D5" s="273" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="207"/>
-      <c r="F5" s="211" t="s">
+      <c r="E5" s="275"/>
+      <c r="F5" s="287" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="211" t="s">
+      <c r="G5" s="280"/>
+      <c r="H5" s="287" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="207"/>
-      <c r="J5" s="217" t="s">
+      <c r="I5" s="275"/>
+      <c r="J5" s="283" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="225"/>
-      <c r="L5" s="197" t="s">
+      <c r="K5" s="305"/>
+      <c r="L5" s="273" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="228"/>
+      <c r="M5" s="308"/>
       <c r="N5" s="111" t="s">
         <v>28</v>
       </c>
@@ -4289,19 +5520,19 @@
       </c>
     </row>
     <row r="6" spans="1:16" s="10" customFormat="1" ht="47.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="202"/>
-      <c r="B6" s="205"/>
-      <c r="C6" s="208"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="208"/>
-      <c r="F6" s="212"/>
-      <c r="G6" s="215"/>
-      <c r="H6" s="213"/>
-      <c r="I6" s="208"/>
-      <c r="J6" s="218"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="198"/>
-      <c r="M6" s="229"/>
+      <c r="A6" s="303"/>
+      <c r="B6" s="304"/>
+      <c r="C6" s="276"/>
+      <c r="D6" s="274"/>
+      <c r="E6" s="276"/>
+      <c r="F6" s="317"/>
+      <c r="G6" s="281"/>
+      <c r="H6" s="288"/>
+      <c r="I6" s="276"/>
+      <c r="J6" s="294"/>
+      <c r="K6" s="306"/>
+      <c r="L6" s="295"/>
+      <c r="M6" s="309"/>
       <c r="N6" s="66" t="s">
         <v>57</v>
       </c>
@@ -4310,22 +5541,22 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="10" customFormat="1" ht="63" x14ac:dyDescent="0.2">
-      <c r="A7" s="202"/>
-      <c r="B7" s="205"/>
-      <c r="C7" s="208"/>
-      <c r="D7" s="210"/>
-      <c r="E7" s="208"/>
-      <c r="F7" s="213"/>
-      <c r="G7" s="215"/>
-      <c r="I7" s="208"/>
+      <c r="A7" s="303"/>
+      <c r="B7" s="304"/>
+      <c r="C7" s="276"/>
+      <c r="D7" s="274"/>
+      <c r="E7" s="276"/>
+      <c r="F7" s="288"/>
+      <c r="G7" s="281"/>
+      <c r="I7" s="276"/>
       <c r="J7" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="226"/>
-      <c r="L7" s="204" t="s">
+      <c r="K7" s="306"/>
+      <c r="L7" s="292" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="229"/>
+      <c r="M7" s="309"/>
       <c r="N7" s="67" t="s">
         <v>61</v>
       </c>
@@ -4334,105 +5565,105 @@
       </c>
     </row>
     <row r="8" spans="1:16" s="10" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="202"/>
-      <c r="B8" s="206"/>
-      <c r="C8" s="208"/>
-      <c r="D8" s="198"/>
-      <c r="E8" s="208"/>
+      <c r="A8" s="303"/>
+      <c r="B8" s="293"/>
+      <c r="C8" s="276"/>
+      <c r="D8" s="295"/>
+      <c r="E8" s="276"/>
       <c r="F8" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="215"/>
-      <c r="I8" s="208"/>
-      <c r="K8" s="226"/>
-      <c r="L8" s="206"/>
-      <c r="M8" s="229"/>
+      <c r="G8" s="281"/>
+      <c r="I8" s="276"/>
+      <c r="K8" s="306"/>
+      <c r="L8" s="293"/>
+      <c r="M8" s="309"/>
       <c r="N8" s="114" t="s">
         <v>70</v>
       </c>
       <c r="P8" s="85"/>
     </row>
     <row r="9" spans="1:16" s="10" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="202"/>
-      <c r="C9" s="208"/>
+      <c r="A9" s="303"/>
+      <c r="C9" s="276"/>
       <c r="D9" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="208"/>
-      <c r="G9" s="215"/>
-      <c r="I9" s="208"/>
+      <c r="E9" s="276"/>
+      <c r="G9" s="281"/>
+      <c r="I9" s="276"/>
       <c r="J9" s="79"/>
-      <c r="K9" s="226"/>
-      <c r="L9" s="211" t="s">
+      <c r="K9" s="306"/>
+      <c r="L9" s="287" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="229"/>
+      <c r="M9" s="309"/>
       <c r="N9" s="150" t="s">
         <v>89</v>
       </c>
       <c r="P9" s="85"/>
     </row>
     <row r="10" spans="1:16" s="10" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="202"/>
-      <c r="C10" s="208"/>
-      <c r="D10" s="211" t="s">
+      <c r="A10" s="303"/>
+      <c r="C10" s="276"/>
+      <c r="D10" s="287" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="208"/>
-      <c r="G10" s="215"/>
-      <c r="I10" s="208"/>
+      <c r="E10" s="276"/>
+      <c r="G10" s="281"/>
+      <c r="I10" s="276"/>
       <c r="J10" s="79"/>
-      <c r="K10" s="226"/>
-      <c r="L10" s="213"/>
-      <c r="M10" s="229"/>
+      <c r="K10" s="306"/>
+      <c r="L10" s="288"/>
+      <c r="M10" s="309"/>
       <c r="N10" s="85"/>
       <c r="P10" s="85"/>
     </row>
     <row r="11" spans="1:16" s="10" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="202"/>
-      <c r="C11" s="208"/>
-      <c r="D11" s="213"/>
-      <c r="E11" s="208"/>
-      <c r="G11" s="215"/>
-      <c r="I11" s="208"/>
-      <c r="K11" s="226"/>
+      <c r="A11" s="303"/>
+      <c r="C11" s="276"/>
+      <c r="D11" s="288"/>
+      <c r="E11" s="276"/>
+      <c r="G11" s="281"/>
+      <c r="I11" s="276"/>
+      <c r="K11" s="306"/>
       <c r="L11" s="114" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="229"/>
+      <c r="M11" s="309"/>
       <c r="N11" s="85"/>
       <c r="P11" s="85"/>
     </row>
     <row r="12" spans="1:16" s="10" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="202"/>
-      <c r="C12" s="208"/>
+      <c r="A12" s="303"/>
+      <c r="C12" s="276"/>
       <c r="D12" s="84"/>
-      <c r="E12" s="208"/>
-      <c r="G12" s="215"/>
-      <c r="I12" s="208"/>
+      <c r="E12" s="276"/>
+      <c r="G12" s="281"/>
+      <c r="I12" s="276"/>
       <c r="J12" s="79"/>
-      <c r="K12" s="226"/>
-      <c r="L12" s="197" t="s">
-        <v>244</v>
-      </c>
-      <c r="M12" s="229"/>
+      <c r="K12" s="306"/>
+      <c r="L12" s="273" t="s">
+        <v>250</v>
+      </c>
+      <c r="M12" s="309"/>
       <c r="N12" s="85"/>
       <c r="P12" s="85"/>
     </row>
     <row r="13" spans="1:16" s="10" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="203"/>
+      <c r="A13" s="303"/>
       <c r="B13" s="82"/>
-      <c r="C13" s="209"/>
+      <c r="C13" s="277"/>
       <c r="D13" s="80"/>
-      <c r="E13" s="209"/>
+      <c r="E13" s="277"/>
       <c r="F13" s="82"/>
-      <c r="G13" s="216"/>
+      <c r="G13" s="282"/>
       <c r="H13" s="82"/>
-      <c r="I13" s="209"/>
+      <c r="I13" s="277"/>
       <c r="J13" s="80"/>
-      <c r="K13" s="227"/>
-      <c r="L13" s="198"/>
-      <c r="M13" s="230"/>
+      <c r="K13" s="307"/>
+      <c r="L13" s="295"/>
+      <c r="M13" s="310"/>
       <c r="N13" s="40"/>
       <c r="O13" s="82"/>
       <c r="P13" s="40"/>
@@ -4451,24 +5682,26 @@
       <c r="N14" s="149"/>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="219">
-        <v>46126</v>
-      </c>
-      <c r="B15" s="223" t="s">
+      <c r="A15" s="303">
+        <v>46122</v>
+      </c>
+      <c r="B15" s="285" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="214"/>
-      <c r="D15" s="217" t="s">
+      <c r="C15" s="280"/>
+      <c r="D15" s="283" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="214"/>
-      <c r="F15" s="204" t="s">
+      <c r="E15" s="280"/>
+      <c r="F15" s="292" t="s">
         <v>24</v>
       </c>
       <c r="G15" s="69"/>
-      <c r="H15" s="194"/>
+      <c r="H15" s="313" t="s">
+        <v>240</v>
+      </c>
       <c r="I15" s="69"/>
-      <c r="J15" s="220" t="s">
+      <c r="J15" s="311" t="s">
         <v>13</v>
       </c>
       <c r="K15" s="71"/>
@@ -4485,16 +5718,16 @@
       </c>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="78.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="219"/>
-      <c r="B16" s="224"/>
-      <c r="C16" s="215"/>
-      <c r="D16" s="222"/>
-      <c r="E16" s="215"/>
-      <c r="F16" s="206"/>
+      <c r="A16" s="303"/>
+      <c r="B16" s="286"/>
+      <c r="C16" s="281"/>
+      <c r="D16" s="284"/>
+      <c r="E16" s="281"/>
+      <c r="F16" s="293"/>
       <c r="G16" s="70"/>
-      <c r="H16" s="195"/>
+      <c r="H16" s="314"/>
       <c r="I16" s="70"/>
-      <c r="J16" s="221"/>
+      <c r="J16" s="312"/>
       <c r="K16" s="72"/>
       <c r="L16" s="77" t="s">
         <v>86</v>
@@ -4508,17 +5741,17 @@
       </c>
     </row>
     <row r="17" spans="1:16" s="10" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="219"/>
+      <c r="A17" s="303"/>
       <c r="B17" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="215"/>
-      <c r="E17" s="215"/>
-      <c r="F17" s="204" t="s">
+      <c r="C17" s="281"/>
+      <c r="E17" s="281"/>
+      <c r="F17" s="292" t="s">
         <v>45</v>
       </c>
       <c r="G17" s="70"/>
-      <c r="H17" s="195"/>
+      <c r="H17" s="314"/>
       <c r="I17" s="70"/>
       <c r="J17" s="111" t="s">
         <v>83</v>
@@ -4534,15 +5767,15 @@
       <c r="P17" s="85"/>
     </row>
     <row r="18" spans="1:16" s="10" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="219"/>
+      <c r="A18" s="303"/>
       <c r="B18" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="215"/>
-      <c r="E18" s="215"/>
-      <c r="F18" s="206"/>
+      <c r="C18" s="281"/>
+      <c r="E18" s="281"/>
+      <c r="F18" s="293"/>
       <c r="G18" s="70"/>
-      <c r="H18" s="195"/>
+      <c r="H18" s="314"/>
       <c r="I18" s="70"/>
       <c r="J18" s="102" t="s">
         <v>99</v>
@@ -4558,15 +5791,15 @@
       <c r="P18" s="85"/>
     </row>
     <row r="19" spans="1:16" s="10" customFormat="1" ht="63" x14ac:dyDescent="0.2">
-      <c r="A19" s="219"/>
+      <c r="A19" s="303"/>
       <c r="B19" s="80"/>
-      <c r="C19" s="215"/>
-      <c r="E19" s="215"/>
+      <c r="C19" s="281"/>
+      <c r="E19" s="281"/>
       <c r="F19" s="114" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="70"/>
-      <c r="H19" s="195"/>
+      <c r="H19" s="314"/>
       <c r="I19" s="70"/>
       <c r="J19" s="67" t="s">
         <v>58</v>
@@ -4577,19 +5810,19 @@
       <c r="P19" s="85"/>
     </row>
     <row r="20" spans="1:16" s="10" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="219"/>
+      <c r="A20" s="303"/>
       <c r="B20" s="114" t="s">
         <v>229</v>
       </c>
-      <c r="C20" s="215"/>
+      <c r="C20" s="281"/>
       <c r="D20" s="114" t="s">
         <v>230</v>
       </c>
-      <c r="E20" s="215"/>
+      <c r="E20" s="281"/>
       <c r="G20" s="70"/>
-      <c r="H20" s="195"/>
+      <c r="H20" s="314"/>
       <c r="I20" s="70"/>
-      <c r="J20" s="217" t="s">
+      <c r="J20" s="283" t="s">
         <v>82</v>
       </c>
       <c r="K20" s="72"/>
@@ -4598,16 +5831,16 @@
       <c r="P20" s="85"/>
     </row>
     <row r="21" spans="1:16" s="10" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="219"/>
+      <c r="A21" s="303"/>
       <c r="B21" s="82"/>
-      <c r="C21" s="216"/>
+      <c r="C21" s="282"/>
       <c r="D21" s="80"/>
-      <c r="E21" s="216"/>
+      <c r="E21" s="282"/>
       <c r="F21" s="40"/>
       <c r="G21" s="81"/>
       <c r="H21" s="80"/>
       <c r="I21" s="81"/>
-      <c r="J21" s="222"/>
+      <c r="J21" s="284"/>
       <c r="K21" s="83"/>
       <c r="L21" s="82"/>
       <c r="M21" s="81"/>
@@ -4616,52 +5849,52 @@
       <c r="P21" s="40"/>
     </row>
     <row r="22" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="237"/>
-      <c r="B22" s="238"/>
-      <c r="C22" s="238"/>
-      <c r="D22" s="238"/>
-      <c r="E22" s="238"/>
-      <c r="F22" s="238"/>
-      <c r="G22" s="238"/>
-      <c r="H22" s="238"/>
-      <c r="I22" s="238"/>
-      <c r="J22" s="238"/>
-      <c r="K22" s="238"/>
-      <c r="L22" s="238"/>
-      <c r="M22" s="238"/>
-      <c r="N22" s="238"/>
-      <c r="O22" s="238"/>
-      <c r="P22" s="239"/>
+      <c r="A22" s="289"/>
+      <c r="B22" s="290"/>
+      <c r="C22" s="290"/>
+      <c r="D22" s="290"/>
+      <c r="E22" s="290"/>
+      <c r="F22" s="290"/>
+      <c r="G22" s="290"/>
+      <c r="H22" s="290"/>
+      <c r="I22" s="290"/>
+      <c r="J22" s="290"/>
+      <c r="K22" s="290"/>
+      <c r="L22" s="290"/>
+      <c r="M22" s="290"/>
+      <c r="N22" s="290"/>
+      <c r="O22" s="290"/>
+      <c r="P22" s="291"/>
     </row>
     <row r="23" spans="1:16" s="10" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="219">
-        <v>46127</v>
-      </c>
-      <c r="B23" s="211" t="s">
+      <c r="A23" s="303">
+        <v>46123</v>
+      </c>
+      <c r="B23" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="207"/>
-      <c r="D23" s="217" t="s">
+      <c r="C23" s="275"/>
+      <c r="D23" s="283" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="207"/>
-      <c r="F23" s="217" t="s">
+      <c r="E23" s="275"/>
+      <c r="F23" s="283" t="s">
         <v>32</v>
       </c>
       <c r="G23" s="69"/>
-      <c r="H23" s="204" t="s">
+      <c r="H23" s="292" t="s">
         <v>55</v>
       </c>
       <c r="I23" s="62"/>
-      <c r="J23" s="197" t="s">
+      <c r="J23" s="273" t="s">
         <v>9</v>
       </c>
       <c r="K23" s="71"/>
-      <c r="L23" s="217" t="s">
+      <c r="L23" s="283" t="s">
         <v>78</v>
       </c>
       <c r="M23" s="64"/>
-      <c r="N23" s="223" t="s">
+      <c r="N23" s="285" t="s">
         <v>16</v>
       </c>
       <c r="O23" s="148"/>
@@ -4670,36 +5903,36 @@
       </c>
     </row>
     <row r="24" spans="1:16" s="10" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="219"/>
-      <c r="B24" s="213"/>
-      <c r="C24" s="208"/>
-      <c r="D24" s="218"/>
-      <c r="E24" s="208"/>
-      <c r="F24" s="222"/>
+      <c r="A24" s="303"/>
+      <c r="B24" s="288"/>
+      <c r="C24" s="276"/>
+      <c r="D24" s="294"/>
+      <c r="E24" s="276"/>
+      <c r="F24" s="284"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="205"/>
+      <c r="H24" s="304"/>
       <c r="I24" s="63"/>
-      <c r="J24" s="210"/>
+      <c r="J24" s="274"/>
       <c r="K24" s="72"/>
-      <c r="L24" s="222"/>
+      <c r="L24" s="284"/>
       <c r="M24" s="65"/>
-      <c r="N24" s="224"/>
+      <c r="N24" s="286"/>
       <c r="P24" s="147" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="10" customFormat="1" ht="94.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="219"/>
+      <c r="A25" s="303"/>
       <c r="B25" s="77" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="208"/>
-      <c r="D25" s="197" t="s">
-        <v>248</v>
-      </c>
-      <c r="E25" s="208"/>
-      <c r="F25" s="197" t="s">
-        <v>250</v>
+      <c r="C25" s="276"/>
+      <c r="D25" s="273" t="s">
+        <v>254</v>
+      </c>
+      <c r="E25" s="276"/>
+      <c r="F25" s="273" t="s">
+        <v>256</v>
       </c>
       <c r="G25" s="70"/>
       <c r="H25" s="67" t="s">
@@ -4720,14 +5953,14 @@
       <c r="P25" s="85"/>
     </row>
     <row r="26" spans="1:16" s="10" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="219"/>
+      <c r="A26" s="303"/>
       <c r="B26" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="208"/>
-      <c r="D26" s="198"/>
-      <c r="E26" s="208"/>
-      <c r="F26" s="198"/>
+      <c r="C26" s="276"/>
+      <c r="D26" s="295"/>
+      <c r="E26" s="276"/>
+      <c r="F26" s="295"/>
       <c r="G26" s="70"/>
       <c r="I26" s="63"/>
       <c r="J26" s="66" t="s">
@@ -4744,19 +5977,19 @@
       <c r="P26" s="85"/>
     </row>
     <row r="27" spans="1:16" s="10" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="219"/>
+      <c r="A27" s="303"/>
       <c r="B27" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="208"/>
+      <c r="C27" s="276"/>
       <c r="D27" s="85"/>
-      <c r="E27" s="208"/>
+      <c r="E27" s="276"/>
       <c r="G27" s="70"/>
       <c r="H27" s="79"/>
       <c r="I27" s="63"/>
       <c r="J27" s="85"/>
       <c r="K27" s="72"/>
-      <c r="L27" s="211" t="s">
+      <c r="L27" s="287" t="s">
         <v>80</v>
       </c>
       <c r="M27" s="65"/>
@@ -4766,18 +5999,18 @@
       <c r="P27" s="85"/>
     </row>
     <row r="28" spans="1:16" s="10" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="219"/>
+      <c r="A28" s="303"/>
       <c r="B28" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="208"/>
+      <c r="C28" s="276"/>
       <c r="D28" s="79"/>
-      <c r="E28" s="208"/>
+      <c r="E28" s="276"/>
       <c r="G28" s="70"/>
       <c r="H28" s="79"/>
       <c r="I28" s="63"/>
       <c r="K28" s="72"/>
-      <c r="L28" s="213"/>
+      <c r="L28" s="288"/>
       <c r="M28" s="65"/>
       <c r="N28" s="102" t="s">
         <v>101</v>
@@ -4785,13 +6018,13 @@
       <c r="P28" s="85"/>
     </row>
     <row r="29" spans="1:16" s="10" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="219"/>
+      <c r="A29" s="303"/>
       <c r="B29" s="114" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="208"/>
+      <c r="C29" s="276"/>
       <c r="D29" s="79"/>
-      <c r="E29" s="208"/>
+      <c r="E29" s="276"/>
       <c r="G29" s="70"/>
       <c r="H29" s="79"/>
       <c r="I29" s="63"/>
@@ -4804,10 +6037,10 @@
       <c r="P29" s="85"/>
     </row>
     <row r="30" spans="1:16" s="10" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="219"/>
-      <c r="C30" s="208"/>
+      <c r="A30" s="303"/>
+      <c r="C30" s="276"/>
       <c r="D30" s="79"/>
-      <c r="E30" s="208"/>
+      <c r="E30" s="276"/>
       <c r="G30" s="70"/>
       <c r="H30" s="79"/>
       <c r="I30" s="63"/>
@@ -4820,10 +6053,10 @@
       <c r="P30" s="85"/>
     </row>
     <row r="31" spans="1:16" s="10" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="219"/>
-      <c r="C31" s="208"/>
+      <c r="A31" s="303"/>
+      <c r="C31" s="276"/>
       <c r="D31" s="79"/>
-      <c r="E31" s="208"/>
+      <c r="E31" s="276"/>
       <c r="G31" s="70"/>
       <c r="H31" s="79"/>
       <c r="I31" s="63"/>
@@ -4836,10 +6069,10 @@
       <c r="P31" s="85"/>
     </row>
     <row r="32" spans="1:16" s="10" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="219"/>
-      <c r="C32" s="208"/>
+      <c r="A32" s="303"/>
+      <c r="C32" s="276"/>
       <c r="D32" s="79"/>
-      <c r="E32" s="208"/>
+      <c r="E32" s="276"/>
       <c r="G32" s="70"/>
       <c r="H32" s="79"/>
       <c r="I32" s="63"/>
@@ -4852,11 +6085,11 @@
       <c r="P32" s="85"/>
     </row>
     <row r="33" spans="1:16" s="10" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="219"/>
+      <c r="A33" s="303"/>
       <c r="B33" s="82"/>
-      <c r="C33" s="209"/>
+      <c r="C33" s="277"/>
       <c r="D33" s="80"/>
-      <c r="E33" s="209"/>
+      <c r="E33" s="277"/>
       <c r="F33" s="82"/>
       <c r="G33" s="81"/>
       <c r="H33" s="80"/>
@@ -4872,50 +6105,50 @@
       <c r="P33" s="40"/>
     </row>
     <row r="34" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="232"/>
-      <c r="B34" s="233"/>
-      <c r="C34" s="233"/>
-      <c r="D34" s="233"/>
-      <c r="E34" s="233"/>
-      <c r="F34" s="233"/>
-      <c r="G34" s="233"/>
-      <c r="H34" s="233"/>
-      <c r="I34" s="233"/>
-      <c r="J34" s="233"/>
-      <c r="K34" s="233"/>
-      <c r="L34" s="233"/>
-      <c r="M34" s="233"/>
-      <c r="N34" s="234"/>
+      <c r="A34" s="297"/>
+      <c r="B34" s="298"/>
+      <c r="C34" s="298"/>
+      <c r="D34" s="298"/>
+      <c r="E34" s="298"/>
+      <c r="F34" s="298"/>
+      <c r="G34" s="298"/>
+      <c r="H34" s="298"/>
+      <c r="I34" s="298"/>
+      <c r="J34" s="298"/>
+      <c r="K34" s="298"/>
+      <c r="L34" s="298"/>
+      <c r="M34" s="298"/>
+      <c r="N34" s="299"/>
     </row>
     <row r="35" spans="1:16" s="10" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="201">
-        <v>46128</v>
-      </c>
-      <c r="B35" s="197" t="s">
+      <c r="A35" s="300">
+        <v>46125</v>
+      </c>
+      <c r="B35" s="273" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="207"/>
+      <c r="C35" s="275"/>
       <c r="D35" s="114" t="s">
         <v>60</v>
       </c>
-      <c r="E35" s="207"/>
-      <c r="F35" s="197" t="s">
+      <c r="E35" s="275"/>
+      <c r="F35" s="273" t="s">
         <v>10</v>
       </c>
-      <c r="G35" s="214"/>
+      <c r="G35" s="280"/>
       <c r="H35" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="I35" s="207"/>
-      <c r="J35" s="204" t="s">
+      <c r="I35" s="275"/>
+      <c r="J35" s="292" t="s">
         <v>47</v>
       </c>
-      <c r="K35" s="214"/>
-      <c r="L35" s="197" t="s">
+      <c r="K35" s="280"/>
+      <c r="L35" s="273" t="s">
         <v>14</v>
       </c>
-      <c r="M35" s="207"/>
-      <c r="N35" s="235" t="s">
+      <c r="M35" s="275"/>
+      <c r="N35" s="278" t="s">
         <v>225</v>
       </c>
       <c r="O35" s="148"/>
@@ -4924,163 +6157,163 @@
       </c>
     </row>
     <row r="36" spans="1:16" s="10" customFormat="1" ht="78.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="202"/>
-      <c r="B36" s="210"/>
-      <c r="C36" s="208"/>
+      <c r="A36" s="301"/>
+      <c r="B36" s="274"/>
+      <c r="C36" s="276"/>
       <c r="D36" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="E36" s="208"/>
-      <c r="F36" s="210"/>
-      <c r="G36" s="215"/>
+      <c r="E36" s="276"/>
+      <c r="F36" s="274"/>
+      <c r="G36" s="281"/>
       <c r="H36" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="I36" s="208"/>
-      <c r="J36" s="206"/>
-      <c r="K36" s="215"/>
-      <c r="L36" s="210"/>
-      <c r="M36" s="208"/>
-      <c r="N36" s="235"/>
+      <c r="I36" s="276"/>
+      <c r="J36" s="293"/>
+      <c r="K36" s="281"/>
+      <c r="L36" s="274"/>
+      <c r="M36" s="276"/>
+      <c r="N36" s="278"/>
       <c r="P36" s="101" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:16" s="10" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="202"/>
+      <c r="A37" s="301"/>
       <c r="B37" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="208"/>
+      <c r="C37" s="276"/>
       <c r="D37" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="208"/>
-      <c r="F37" s="211" t="s">
+      <c r="E37" s="276"/>
+      <c r="F37" s="287" t="s">
         <v>40</v>
       </c>
-      <c r="G37" s="215"/>
+      <c r="G37" s="281"/>
       <c r="H37" s="66" t="s">
         <v>104</v>
       </c>
-      <c r="I37" s="208"/>
+      <c r="I37" s="276"/>
       <c r="J37" s="112" t="s">
         <v>30</v>
       </c>
-      <c r="K37" s="215"/>
+      <c r="K37" s="281"/>
       <c r="L37" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="M37" s="208"/>
+      <c r="M37" s="276"/>
       <c r="N37" s="66" t="s">
         <v>53</v>
       </c>
       <c r="P37" s="85"/>
     </row>
     <row r="38" spans="1:16" s="10" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="202"/>
-      <c r="B38" s="236" t="s">
+      <c r="A38" s="301"/>
+      <c r="B38" s="279" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="208"/>
-      <c r="E38" s="208"/>
-      <c r="F38" s="213"/>
-      <c r="G38" s="215"/>
+      <c r="C38" s="276"/>
+      <c r="E38" s="276"/>
+      <c r="F38" s="288"/>
+      <c r="G38" s="281"/>
       <c r="H38" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="I38" s="208"/>
+      <c r="I38" s="276"/>
       <c r="J38" s="114" t="s">
         <v>33</v>
       </c>
-      <c r="K38" s="215"/>
+      <c r="K38" s="281"/>
       <c r="L38" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="M38" s="208"/>
+      <c r="M38" s="276"/>
       <c r="N38" s="111" t="s">
         <v>51</v>
       </c>
       <c r="P38" s="85"/>
     </row>
     <row r="39" spans="1:16" s="10" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="202"/>
-      <c r="B39" s="236"/>
-      <c r="C39" s="208"/>
-      <c r="E39" s="208"/>
+      <c r="A39" s="301"/>
+      <c r="B39" s="279"/>
+      <c r="C39" s="276"/>
+      <c r="E39" s="276"/>
       <c r="F39" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="G39" s="215"/>
+      <c r="G39" s="281"/>
       <c r="H39" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="I39" s="208"/>
+      <c r="I39" s="276"/>
       <c r="J39" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="K39" s="215"/>
+      <c r="K39" s="281"/>
       <c r="L39" s="114" t="s">
         <v>66</v>
       </c>
-      <c r="M39" s="208"/>
+      <c r="M39" s="276"/>
       <c r="N39" s="114" t="s">
         <v>71</v>
       </c>
       <c r="P39" s="85"/>
     </row>
     <row r="40" spans="1:16" s="10" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="202"/>
-      <c r="C40" s="208"/>
-      <c r="E40" s="208"/>
-      <c r="G40" s="215"/>
+      <c r="A40" s="301"/>
+      <c r="C40" s="276"/>
+      <c r="E40" s="276"/>
+      <c r="G40" s="281"/>
       <c r="H40" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="I40" s="208"/>
+      <c r="I40" s="276"/>
       <c r="J40" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="K40" s="215"/>
-      <c r="M40" s="208"/>
+      <c r="K40" s="281"/>
+      <c r="M40" s="276"/>
       <c r="N40" s="120" t="s">
         <v>98</v>
       </c>
       <c r="P40" s="85"/>
     </row>
     <row r="41" spans="1:16" s="10" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="202"/>
-      <c r="C41" s="208"/>
-      <c r="E41" s="208"/>
-      <c r="G41" s="215"/>
+      <c r="A41" s="301"/>
+      <c r="C41" s="276"/>
+      <c r="E41" s="276"/>
+      <c r="G41" s="281"/>
       <c r="H41" s="102" t="s">
         <v>108</v>
       </c>
-      <c r="I41" s="208"/>
+      <c r="I41" s="276"/>
       <c r="J41" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="K41" s="215"/>
-      <c r="M41" s="208"/>
+      <c r="K41" s="281"/>
+      <c r="M41" s="276"/>
       <c r="N41" s="121" t="s">
         <v>224</v>
       </c>
       <c r="P41" s="85"/>
     </row>
     <row r="42" spans="1:16" s="10" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="202"/>
+      <c r="A42" s="301"/>
       <c r="B42" s="79"/>
-      <c r="C42" s="208"/>
+      <c r="C42" s="276"/>
       <c r="D42" s="104"/>
-      <c r="E42" s="208"/>
+      <c r="E42" s="276"/>
       <c r="F42" s="104"/>
-      <c r="G42" s="215"/>
+      <c r="G42" s="281"/>
       <c r="H42" s="104"/>
-      <c r="I42" s="208"/>
+      <c r="I42" s="276"/>
       <c r="J42" s="104"/>
-      <c r="K42" s="215"/>
+      <c r="K42" s="281"/>
       <c r="L42" s="104"/>
-      <c r="M42" s="208"/>
+      <c r="M42" s="276"/>
       <c r="N42" s="103" t="s">
         <v>92</v>
       </c>
@@ -5088,40 +6321,40 @@
       <c r="P42" s="79"/>
     </row>
     <row r="43" spans="1:16" s="10" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="203"/>
+      <c r="A43" s="302"/>
       <c r="B43" s="155"/>
-      <c r="C43" s="209"/>
+      <c r="C43" s="277"/>
       <c r="D43" s="155"/>
-      <c r="E43" s="209"/>
+      <c r="E43" s="277"/>
       <c r="F43" s="155"/>
-      <c r="G43" s="216"/>
+      <c r="G43" s="282"/>
       <c r="H43" s="155"/>
-      <c r="I43" s="209"/>
+      <c r="I43" s="277"/>
       <c r="J43" s="155"/>
-      <c r="K43" s="216"/>
+      <c r="K43" s="282"/>
       <c r="L43" s="155"/>
-      <c r="M43" s="209"/>
+      <c r="M43" s="277"/>
       <c r="N43" s="156"/>
       <c r="O43" s="155"/>
       <c r="P43" s="80"/>
     </row>
     <row r="44" spans="1:16" s="10" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="231" t="s">
-        <v>263</v>
-      </c>
-      <c r="B44" s="231"/>
-      <c r="C44" s="231"/>
-      <c r="D44" s="231"/>
-      <c r="E44" s="231"/>
-      <c r="F44" s="231"/>
-      <c r="G44" s="231"/>
-      <c r="H44" s="231"/>
-      <c r="I44" s="231"/>
-      <c r="J44" s="231"/>
-      <c r="K44" s="231"/>
-      <c r="L44" s="231"/>
-      <c r="M44" s="231"/>
-      <c r="N44" s="231"/>
+      <c r="A44" s="296" t="s">
+        <v>270</v>
+      </c>
+      <c r="B44" s="296"/>
+      <c r="C44" s="296"/>
+      <c r="D44" s="296"/>
+      <c r="E44" s="296"/>
+      <c r="F44" s="296"/>
+      <c r="G44" s="296"/>
+      <c r="H44" s="296"/>
+      <c r="I44" s="296"/>
+      <c r="J44" s="296"/>
+      <c r="K44" s="296"/>
+      <c r="L44" s="296"/>
+      <c r="M44" s="296"/>
+      <c r="N44" s="296"/>
     </row>
     <row r="45" spans="1:16" s="10" customFormat="1" ht="27.75" x14ac:dyDescent="0.3">
       <c r="A45" s="47"/>
@@ -5155,7 +6388,51 @@
       <c r="J47" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="60">
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C13"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E13"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G13"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I13"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="A15:A21"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="H15:H20"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="K5:K13"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M13"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="I35:I43"/>
+    <mergeCell ref="K35:K43"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="A35:A43"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="A23:A33"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C33"/>
+    <mergeCell ref="E23:E33"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="H23:H24"/>
     <mergeCell ref="L35:L36"/>
     <mergeCell ref="M35:M43"/>
     <mergeCell ref="N35:N36"/>
@@ -5172,267 +6449,3453 @@
     <mergeCell ref="A22:P22"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="I35:I43"/>
-    <mergeCell ref="K35:K43"/>
-    <mergeCell ref="A44:N44"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="A35:A43"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="A23:A33"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C33"/>
-    <mergeCell ref="E23:E33"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="K5:K13"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M13"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A15:A21"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C13"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E13"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G13"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I13"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="L12:L13"/>
   </mergeCells>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="85" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="83" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50">
-    <cfRule type="duplicateValues" dxfId="82" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="80" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="79" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="78" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="77" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46">
-    <cfRule type="duplicateValues" dxfId="76" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="75" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48">
-    <cfRule type="duplicateValues" dxfId="74" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50">
-    <cfRule type="duplicateValues" dxfId="73" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C51">
-    <cfRule type="duplicateValues" dxfId="72" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C52">
-    <cfRule type="duplicateValues" dxfId="71" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54">
-    <cfRule type="duplicateValues" dxfId="70" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C55">
-    <cfRule type="duplicateValues" dxfId="69" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C86">
-    <cfRule type="duplicateValues" dxfId="68" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C87">
-    <cfRule type="duplicateValues" dxfId="67" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C88">
-    <cfRule type="duplicateValues" dxfId="66" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90">
-    <cfRule type="duplicateValues" dxfId="65" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C91">
-    <cfRule type="duplicateValues" dxfId="64" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="duplicateValues" dxfId="63" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48">
-    <cfRule type="duplicateValues" dxfId="61" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="duplicateValues" dxfId="59" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="duplicateValues" dxfId="57" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D62">
-    <cfRule type="duplicateValues" dxfId="55" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63">
-    <cfRule type="duplicateValues" dxfId="53" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D66">
-    <cfRule type="duplicateValues" dxfId="51" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67">
-    <cfRule type="duplicateValues" dxfId="49" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87">
-    <cfRule type="duplicateValues" dxfId="47" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D88">
-    <cfRule type="duplicateValues" dxfId="45" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D89">
-    <cfRule type="duplicateValues" dxfId="43" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D90">
-    <cfRule type="duplicateValues" dxfId="41" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D91">
-    <cfRule type="duplicateValues" dxfId="39" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D92">
-    <cfRule type="duplicateValues" dxfId="37" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61">
-    <cfRule type="duplicateValues" dxfId="35" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61:E66">
-    <cfRule type="duplicateValues" dxfId="34" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62">
-    <cfRule type="duplicateValues" dxfId="33" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62:E66">
-    <cfRule type="duplicateValues" dxfId="32" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65">
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65:E70">
-    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E66">
-    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E66:E70">
-    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L60">
-    <cfRule type="duplicateValues" dxfId="27" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L62">
-    <cfRule type="duplicateValues" dxfId="25" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L63">
-    <cfRule type="duplicateValues" dxfId="23" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L64">
-    <cfRule type="duplicateValues" dxfId="21" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L66">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67">
-    <cfRule type="duplicateValues" dxfId="17" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M62">
-    <cfRule type="duplicateValues" dxfId="15" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M62:M65">
-    <cfRule type="duplicateValues" dxfId="14" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M62:M66">
-    <cfRule type="duplicateValues" dxfId="13" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M63">
-    <cfRule type="duplicateValues" dxfId="12" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M63:M65">
-    <cfRule type="duplicateValues" dxfId="11" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M63:M66">
-    <cfRule type="duplicateValues" dxfId="10" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66">
-    <cfRule type="duplicateValues" dxfId="9" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66:M69">
-    <cfRule type="duplicateValues" dxfId="8" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66:M70">
-    <cfRule type="duplicateValues" dxfId="7" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67">
-    <cfRule type="duplicateValues" dxfId="6" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67:M69">
-    <cfRule type="duplicateValues" dxfId="5" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67:M70">
-    <cfRule type="duplicateValues" dxfId="4" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N54">
-    <cfRule type="duplicateValues" dxfId="3" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N58">
-    <cfRule type="duplicateValues" dxfId="1" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="112"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F125"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="58.5703125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="2.7109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="45.85546875" style="18" customWidth="1"/>
+    <col min="5" max="5" width="2.7109375" style="18" customWidth="1"/>
+    <col min="6" max="6" width="61.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="9.140625" style="18"/>
+    <col min="11" max="11" width="38.28515625" style="18" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="318" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="319"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="320"/>
+    </row>
+    <row r="2" spans="1:6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="321" t="s">
+        <v>275</v>
+      </c>
+      <c r="B2" s="322"/>
+      <c r="C2" s="322"/>
+      <c r="D2" s="322"/>
+      <c r="E2" s="322"/>
+      <c r="F2" s="323"/>
+    </row>
+    <row r="3" spans="1:6" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="324" t="s">
+        <v>390</v>
+      </c>
+      <c r="B3" s="325"/>
+      <c r="C3" s="325"/>
+      <c r="D3" s="325"/>
+      <c r="E3" s="220"/>
+      <c r="F3" s="267" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53" t="s">
+        <v>273</v>
+      </c>
+      <c r="E4" s="225"/>
+      <c r="F4" s="53" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="303">
+        <v>46160</v>
+      </c>
+      <c r="B5" s="292" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="268"/>
+      <c r="D5" s="273" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="268"/>
+      <c r="F5" s="102" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="303"/>
+      <c r="B6" s="304"/>
+      <c r="C6" s="268"/>
+      <c r="D6" s="274"/>
+      <c r="E6" s="268"/>
+      <c r="F6" s="226" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="303"/>
+      <c r="B7" s="113" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="268"/>
+      <c r="D7" s="114" t="s">
+        <v>347</v>
+      </c>
+      <c r="E7" s="268"/>
+      <c r="F7" s="101" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="12" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="303"/>
+      <c r="B8" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="268"/>
+      <c r="D8" s="114" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="268"/>
+      <c r="F8" s="237" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="12" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="303"/>
+      <c r="B9" s="111" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="268"/>
+      <c r="D9" s="269"/>
+      <c r="E9" s="268"/>
+      <c r="F9" s="270"/>
+    </row>
+    <row r="10" spans="1:6" s="12" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="303"/>
+      <c r="B10" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="268"/>
+      <c r="D10" s="269"/>
+      <c r="E10" s="268"/>
+      <c r="F10" s="269"/>
+    </row>
+    <row r="11" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="198"/>
+      <c r="B11" s="199"/>
+      <c r="C11" s="200"/>
+      <c r="D11" s="200"/>
+      <c r="E11" s="200"/>
+      <c r="F11" s="211"/>
+    </row>
+    <row r="12" spans="1:6" s="12" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="303">
+        <v>46161</v>
+      </c>
+      <c r="B12" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="311" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="101" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="12" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="303"/>
+      <c r="B13" s="113" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="312"/>
+      <c r="F13" s="236" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="12" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="303"/>
+      <c r="B14" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="150" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="12" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="303"/>
+      <c r="B15" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="203"/>
+    </row>
+    <row r="16" spans="1:6" s="12" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="303"/>
+      <c r="B16" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="101" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="203"/>
+    </row>
+    <row r="17" spans="1:6" s="12" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="303"/>
+      <c r="B17" s="110" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="203"/>
+      <c r="F17" s="203"/>
+    </row>
+    <row r="18" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="199"/>
+      <c r="B18" s="200"/>
+      <c r="C18" s="200"/>
+      <c r="D18" s="200"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="201"/>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="303">
+        <v>46162</v>
+      </c>
+      <c r="B19" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="232"/>
+      <c r="D19" s="273" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="232"/>
+      <c r="F19" s="101" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="12" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="303"/>
+      <c r="B20" s="114" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="274"/>
+      <c r="F20" s="147" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="12" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="303"/>
+      <c r="B21" s="110" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="114" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="103" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="12" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="303"/>
+      <c r="B22" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="203"/>
+    </row>
+    <row r="23" spans="1:6" s="12" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="303"/>
+      <c r="B23" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="218" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="203"/>
+    </row>
+    <row r="24" spans="1:6" s="12" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="303"/>
+      <c r="D24" s="111" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="203"/>
+    </row>
+    <row r="25" spans="1:6" s="12" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="303"/>
+      <c r="B25" s="145"/>
+      <c r="D25" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="F25" s="203"/>
+    </row>
+    <row r="26" spans="1:6" s="12" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="303"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="233"/>
+      <c r="D26" s="237" t="s">
+        <v>358</v>
+      </c>
+      <c r="E26" s="233"/>
+      <c r="F26" s="204"/>
+    </row>
+    <row r="27" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="199"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="200"/>
+      <c r="D27" s="200"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="211"/>
+    </row>
+    <row r="28" spans="1:6" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="300">
+        <v>46163</v>
+      </c>
+      <c r="B28" s="274" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="275"/>
+      <c r="D28" s="273" t="s">
+        <v>254</v>
+      </c>
+      <c r="E28" s="275"/>
+      <c r="F28" s="101" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="301"/>
+      <c r="B29" s="295"/>
+      <c r="C29" s="276"/>
+      <c r="D29" s="295"/>
+      <c r="E29" s="276"/>
+      <c r="F29" s="147" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="301"/>
+      <c r="B30" s="292" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="276"/>
+      <c r="D30" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="276"/>
+      <c r="F30" s="203"/>
+    </row>
+    <row r="31" spans="1:6" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="301"/>
+      <c r="B31" s="293"/>
+      <c r="C31" s="276"/>
+      <c r="D31" s="283" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" s="276"/>
+      <c r="F31" s="203"/>
+    </row>
+    <row r="32" spans="1:6" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="301"/>
+      <c r="B32" s="66" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="276"/>
+      <c r="D32" s="284"/>
+      <c r="E32" s="276"/>
+      <c r="F32" s="203"/>
+    </row>
+    <row r="33" spans="1:6" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="301"/>
+      <c r="B33" s="114" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="276"/>
+      <c r="D33" s="226" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" s="276"/>
+      <c r="F33" s="203"/>
+    </row>
+    <row r="34" spans="1:6" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="301"/>
+      <c r="C34" s="276"/>
+      <c r="D34" s="237" t="s">
+        <v>353</v>
+      </c>
+      <c r="E34" s="276"/>
+      <c r="F34" s="204"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="212"/>
+      <c r="B35" s="202"/>
+      <c r="C35" s="202"/>
+      <c r="D35" s="202"/>
+      <c r="E35" s="202"/>
+      <c r="F35" s="213"/>
+    </row>
+    <row r="36" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="301">
+        <v>46164</v>
+      </c>
+      <c r="B36" s="114" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="281"/>
+      <c r="D36" s="326" t="s">
+        <v>350</v>
+      </c>
+      <c r="E36" s="176"/>
+      <c r="F36" s="231" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="301"/>
+      <c r="B37" s="77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="281"/>
+      <c r="D37" s="326"/>
+      <c r="E37" s="167"/>
+      <c r="F37" s="103" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="301"/>
+      <c r="C38" s="281"/>
+      <c r="D38" s="111" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="167"/>
+      <c r="F38" s="237" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="301"/>
+      <c r="C39" s="281"/>
+      <c r="D39" s="237" t="s">
+        <v>352</v>
+      </c>
+      <c r="E39" s="167"/>
+      <c r="F39" s="247"/>
+    </row>
+    <row r="40" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="301"/>
+      <c r="C40" s="281"/>
+      <c r="D40" s="246" t="s">
+        <v>371</v>
+      </c>
+      <c r="E40" s="167"/>
+      <c r="F40" s="167"/>
+    </row>
+    <row r="41" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="212"/>
+      <c r="B41" s="200"/>
+      <c r="C41" s="200"/>
+      <c r="D41" s="272"/>
+      <c r="E41" s="202"/>
+      <c r="F41" s="213"/>
+    </row>
+    <row r="42" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="300">
+        <v>46165</v>
+      </c>
+      <c r="B42" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="228"/>
+      <c r="D42" s="273" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="176"/>
+      <c r="F42" s="242" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="301"/>
+      <c r="B43" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="194"/>
+      <c r="D43" s="295"/>
+      <c r="E43" s="167"/>
+      <c r="F43" s="103" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="301"/>
+      <c r="B44" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="194"/>
+      <c r="D44" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="167"/>
+      <c r="F44" s="167"/>
+    </row>
+    <row r="45" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="301"/>
+      <c r="B45" s="66" t="s">
+        <v>271</v>
+      </c>
+      <c r="C45" s="194"/>
+      <c r="D45" s="114" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="167"/>
+      <c r="F45" s="167"/>
+    </row>
+    <row r="46" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="301"/>
+      <c r="B46" s="110" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="194"/>
+      <c r="D46" s="66" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" s="167"/>
+      <c r="F46" s="167"/>
+    </row>
+    <row r="47" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="301"/>
+      <c r="B47" s="66" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="194"/>
+      <c r="D47" s="102" t="s">
+        <v>112</v>
+      </c>
+      <c r="E47" s="167"/>
+      <c r="F47" s="167"/>
+    </row>
+    <row r="48" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="301"/>
+      <c r="B48" s="66" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="194"/>
+      <c r="D48" s="237" t="s">
+        <v>355</v>
+      </c>
+      <c r="E48" s="167"/>
+      <c r="F48" s="167"/>
+    </row>
+    <row r="49" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="302"/>
+      <c r="C49" s="229"/>
+      <c r="D49" s="239" t="s">
+        <v>369</v>
+      </c>
+      <c r="E49" s="230"/>
+      <c r="F49" s="230"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="206"/>
+      <c r="B50" s="200"/>
+      <c r="C50" s="200"/>
+      <c r="D50" s="200"/>
+      <c r="E50" s="202"/>
+      <c r="F50" s="213"/>
+    </row>
+    <row r="51" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="300">
+        <v>46174</v>
+      </c>
+      <c r="B51" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="194"/>
+      <c r="D51" s="237" t="s">
+        <v>356</v>
+      </c>
+      <c r="F51" s="176"/>
+    </row>
+    <row r="52" spans="1:6" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="301"/>
+      <c r="B52" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" s="194"/>
+      <c r="D52" s="237" t="s">
+        <v>357</v>
+      </c>
+      <c r="F52" s="167"/>
+    </row>
+    <row r="53" spans="1:6" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="301"/>
+      <c r="B53" s="207" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="194"/>
+      <c r="D53" s="237" t="s">
+        <v>354</v>
+      </c>
+      <c r="F53" s="167"/>
+    </row>
+    <row r="54" spans="1:6" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="301"/>
+      <c r="B54" s="214" t="s">
+        <v>335</v>
+      </c>
+      <c r="C54" s="194"/>
+      <c r="D54" s="292" t="s">
+        <v>291</v>
+      </c>
+      <c r="F54" s="167"/>
+    </row>
+    <row r="55" spans="1:6" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="301"/>
+      <c r="B55" s="214" t="s">
+        <v>336</v>
+      </c>
+      <c r="C55" s="194"/>
+      <c r="D55" s="293"/>
+      <c r="F55" s="230"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="212"/>
+      <c r="B56" s="200"/>
+      <c r="C56" s="200"/>
+      <c r="D56" s="200"/>
+      <c r="E56" s="202"/>
+      <c r="F56" s="213"/>
+    </row>
+    <row r="57" spans="1:6" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="300">
+        <v>46175</v>
+      </c>
+      <c r="B57" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" s="305"/>
+      <c r="D57" s="273" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="160"/>
+      <c r="F57" s="106"/>
+    </row>
+    <row r="58" spans="1:6" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="301"/>
+      <c r="B58" s="195" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" s="306"/>
+      <c r="D58" s="295"/>
+      <c r="F58" s="109"/>
+    </row>
+    <row r="59" spans="1:6" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="301"/>
+      <c r="B59" s="66" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" s="306"/>
+      <c r="D59" s="237" t="s">
+        <v>368</v>
+      </c>
+      <c r="F59" s="109"/>
+    </row>
+    <row r="60" spans="1:6" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="301"/>
+      <c r="B60" s="114" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="306"/>
+      <c r="D60" s="237" t="s">
+        <v>360</v>
+      </c>
+      <c r="F60" s="109"/>
+    </row>
+    <row r="61" spans="1:6" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="301"/>
+      <c r="B61" s="66" t="s">
+        <v>295</v>
+      </c>
+      <c r="C61" s="306"/>
+      <c r="D61" s="109"/>
+      <c r="F61" s="107"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="240"/>
+      <c r="B62" s="144"/>
+      <c r="C62" s="144"/>
+      <c r="D62" s="144"/>
+      <c r="E62" s="144"/>
+      <c r="F62" s="241"/>
+    </row>
+    <row r="63" spans="1:6" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="301">
+        <v>46176</v>
+      </c>
+      <c r="B63" s="292" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="197"/>
+      <c r="D63" s="287" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="176"/>
+    </row>
+    <row r="64" spans="1:6" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="301"/>
+      <c r="B64" s="293"/>
+      <c r="C64" s="197"/>
+      <c r="D64" s="317"/>
+      <c r="F64" s="167"/>
+    </row>
+    <row r="65" spans="1:6" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="301"/>
+      <c r="B65" s="285" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" s="197"/>
+      <c r="D65" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="F65" s="167"/>
+    </row>
+    <row r="66" spans="1:6" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="301"/>
+      <c r="B66" s="286"/>
+      <c r="C66" s="197"/>
+      <c r="F66" s="167"/>
+    </row>
+    <row r="67" spans="1:6" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="301"/>
+      <c r="B67" s="66" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" s="197"/>
+      <c r="D67" s="237" t="s">
+        <v>361</v>
+      </c>
+      <c r="F67" s="167"/>
+    </row>
+    <row r="68" spans="1:6" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="301"/>
+      <c r="B68" s="216" t="s">
+        <v>337</v>
+      </c>
+      <c r="C68" s="197"/>
+      <c r="D68" s="216" t="s">
+        <v>338</v>
+      </c>
+      <c r="F68" s="230"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="212"/>
+      <c r="B69" s="201"/>
+      <c r="C69" s="217"/>
+      <c r="D69" s="217"/>
+      <c r="E69" s="202"/>
+      <c r="F69" s="213"/>
+    </row>
+    <row r="70" spans="1:6" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="334">
+        <v>46177</v>
+      </c>
+      <c r="B70" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" s="264"/>
+      <c r="D70" s="273" t="s">
+        <v>298</v>
+      </c>
+      <c r="F70" s="176"/>
+    </row>
+    <row r="71" spans="1:6" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="299"/>
+      <c r="B71" s="114" t="s">
+        <v>302</v>
+      </c>
+      <c r="C71" s="265"/>
+      <c r="D71" s="295"/>
+      <c r="F71" s="167"/>
+    </row>
+    <row r="72" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="299"/>
+      <c r="B72" s="167"/>
+      <c r="C72" s="265"/>
+      <c r="D72" s="67" t="s">
+        <v>297</v>
+      </c>
+      <c r="F72" s="167"/>
+    </row>
+    <row r="73" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="299"/>
+      <c r="C73" s="235"/>
+      <c r="D73" s="114" t="s">
+        <v>287</v>
+      </c>
+      <c r="F73" s="167"/>
+    </row>
+    <row r="74" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="299"/>
+      <c r="C74" s="235"/>
+      <c r="D74" s="67" t="s">
+        <v>288</v>
+      </c>
+      <c r="F74" s="167"/>
+    </row>
+    <row r="75" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="299"/>
+      <c r="C75" s="235"/>
+      <c r="D75" s="216" t="s">
+        <v>396</v>
+      </c>
+      <c r="F75" s="167"/>
+    </row>
+    <row r="76" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="299"/>
+      <c r="C76" s="235"/>
+      <c r="D76" s="216" t="s">
+        <v>397</v>
+      </c>
+      <c r="F76" s="167"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="327"/>
+      <c r="B77" s="328"/>
+      <c r="C77" s="328"/>
+      <c r="D77" s="328"/>
+      <c r="E77" s="328"/>
+      <c r="F77" s="329"/>
+    </row>
+    <row r="78" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="334">
+        <v>46178</v>
+      </c>
+      <c r="B78" s="304" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="280"/>
+      <c r="D78" s="114" t="s">
+        <v>66</v>
+      </c>
+      <c r="F78" s="176"/>
+    </row>
+    <row r="79" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="299"/>
+      <c r="B79" s="304"/>
+      <c r="C79" s="281"/>
+      <c r="D79" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="F79" s="167"/>
+    </row>
+    <row r="80" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="299"/>
+      <c r="B80" s="110" t="s">
+        <v>339</v>
+      </c>
+      <c r="C80" s="281"/>
+      <c r="D80" s="210" t="s">
+        <v>91</v>
+      </c>
+      <c r="F80" s="167"/>
+    </row>
+    <row r="81" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="299"/>
+      <c r="B81" s="66" t="s">
+        <v>299</v>
+      </c>
+      <c r="C81" s="281"/>
+      <c r="D81" s="271" t="s">
+        <v>371</v>
+      </c>
+      <c r="F81" s="167"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="212"/>
+      <c r="B82" s="201"/>
+      <c r="C82" s="217"/>
+      <c r="D82" s="217"/>
+      <c r="E82" s="202"/>
+      <c r="F82" s="213"/>
+    </row>
+    <row r="83" spans="1:6" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="334">
+        <v>46179</v>
+      </c>
+      <c r="B83" s="294" t="s">
+        <v>64</v>
+      </c>
+      <c r="D83" s="112" t="s">
+        <v>47</v>
+      </c>
+      <c r="F83" s="176"/>
+    </row>
+    <row r="84" spans="1:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="299"/>
+      <c r="B84" s="294"/>
+      <c r="D84" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="F84" s="167"/>
+    </row>
+    <row r="85" spans="1:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="299"/>
+      <c r="B85" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" s="114" t="s">
+        <v>351</v>
+      </c>
+      <c r="F85" s="109"/>
+    </row>
+    <row r="86" spans="1:6" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="299"/>
+      <c r="B86" s="114" t="s">
+        <v>286</v>
+      </c>
+      <c r="D86" s="77" t="s">
+        <v>348</v>
+      </c>
+      <c r="F86" s="109"/>
+    </row>
+    <row r="87" spans="1:6" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="299"/>
+      <c r="B87" s="67" t="s">
+        <v>289</v>
+      </c>
+      <c r="D87" s="246"/>
+      <c r="F87" s="167"/>
+    </row>
+    <row r="88" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="330"/>
+      <c r="B88" s="330"/>
+      <c r="C88" s="330"/>
+      <c r="D88" s="330"/>
+      <c r="E88" s="330"/>
+      <c r="F88" s="330"/>
+    </row>
+    <row r="89" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="334">
+        <v>46181</v>
+      </c>
+      <c r="B89" s="208" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="106"/>
+      <c r="F89" s="176"/>
+    </row>
+    <row r="90" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="299"/>
+      <c r="B90" s="209" t="s">
+        <v>226</v>
+      </c>
+      <c r="D90" s="107"/>
+      <c r="F90" s="167"/>
+    </row>
+    <row r="91" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="299"/>
+      <c r="B91" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91" s="326" t="s">
+        <v>341</v>
+      </c>
+      <c r="F91" s="167"/>
+    </row>
+    <row r="92" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="299"/>
+      <c r="B92" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="D92" s="326"/>
+      <c r="F92" s="167"/>
+    </row>
+    <row r="93" spans="1:6" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="299"/>
+      <c r="B93" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="D93" s="216" t="s">
+        <v>342</v>
+      </c>
+      <c r="F93" s="167"/>
+    </row>
+    <row r="94" spans="1:6" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="299"/>
+      <c r="B94" s="216" t="s">
+        <v>340</v>
+      </c>
+      <c r="D94" s="230"/>
+      <c r="F94" s="167"/>
+    </row>
+    <row r="95" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="212"/>
+      <c r="B95" s="227"/>
+      <c r="C95" s="217"/>
+      <c r="D95" s="217"/>
+      <c r="E95" s="202"/>
+      <c r="F95" s="213"/>
+    </row>
+    <row r="96" spans="1:6" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="300">
+        <v>46182</v>
+      </c>
+      <c r="B96" s="283" t="s">
+        <v>82</v>
+      </c>
+      <c r="D96" s="176"/>
+      <c r="F96" s="176"/>
+    </row>
+    <row r="97" spans="1:6" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="301"/>
+      <c r="B97" s="294"/>
+      <c r="D97" s="167"/>
+      <c r="F97" s="167"/>
+    </row>
+    <row r="98" spans="1:6" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="301"/>
+      <c r="B98" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="D98" s="167"/>
+      <c r="F98" s="109"/>
+    </row>
+    <row r="99" spans="1:6" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="301"/>
+      <c r="B99" s="114" t="s">
+        <v>38</v>
+      </c>
+      <c r="D99" s="292" t="s">
+        <v>296</v>
+      </c>
+      <c r="F99" s="109"/>
+    </row>
+    <row r="100" spans="1:6" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="301"/>
+      <c r="B100" s="114" t="s">
+        <v>71</v>
+      </c>
+      <c r="D100" s="293"/>
+      <c r="F100" s="109"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="212"/>
+      <c r="B101" s="201"/>
+      <c r="C101" s="217"/>
+      <c r="D101" s="217"/>
+      <c r="E101" s="202"/>
+      <c r="F101" s="213"/>
+    </row>
+    <row r="102" spans="1:6" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="331">
+        <v>46183</v>
+      </c>
+      <c r="B102" s="110" t="s">
+        <v>114</v>
+      </c>
+      <c r="D102" s="111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" s="176"/>
+    </row>
+    <row r="103" spans="1:6" ht="78.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="298"/>
+      <c r="B103" s="77" t="s">
+        <v>86</v>
+      </c>
+      <c r="D103" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="F103" s="167"/>
+    </row>
+    <row r="104" spans="1:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="298"/>
+      <c r="B104" s="114" t="s">
+        <v>113</v>
+      </c>
+      <c r="D104" s="167"/>
+      <c r="F104" s="167"/>
+    </row>
+    <row r="105" spans="1:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="298"/>
+      <c r="B105" s="167"/>
+      <c r="D105" s="230"/>
+      <c r="F105" s="167"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="212"/>
+      <c r="B106" s="201"/>
+      <c r="C106" s="217"/>
+      <c r="D106" s="217"/>
+      <c r="E106" s="202"/>
+      <c r="F106" s="213"/>
+    </row>
+    <row r="107" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="331">
+        <v>46184</v>
+      </c>
+      <c r="B107" s="66" t="s">
+        <v>35</v>
+      </c>
+      <c r="D107" s="77" t="s">
+        <v>343</v>
+      </c>
+      <c r="F107" s="176"/>
+    </row>
+    <row r="108" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="298"/>
+      <c r="B108" s="67" t="s">
+        <v>294</v>
+      </c>
+      <c r="D108" s="114" t="s">
+        <v>349</v>
+      </c>
+      <c r="F108" s="167"/>
+    </row>
+    <row r="109" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="298"/>
+      <c r="B109" s="114" t="s">
+        <v>304</v>
+      </c>
+      <c r="D109" s="79"/>
+      <c r="F109" s="230"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="212"/>
+      <c r="B110" s="201"/>
+      <c r="C110" s="217"/>
+      <c r="D110" s="217"/>
+      <c r="E110" s="202"/>
+      <c r="F110" s="213"/>
+    </row>
+    <row r="111" spans="1:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="331">
+        <v>46185</v>
+      </c>
+      <c r="B111" s="283" t="s">
+        <v>28</v>
+      </c>
+      <c r="D111" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F111" s="176"/>
+    </row>
+    <row r="112" spans="1:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="298"/>
+      <c r="B112" s="284"/>
+      <c r="D112" s="114" t="s">
+        <v>33</v>
+      </c>
+      <c r="F112" s="167"/>
+    </row>
+    <row r="113" spans="1:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="298"/>
+      <c r="B113" s="285" t="s">
+        <v>290</v>
+      </c>
+      <c r="D113" s="113" t="s">
+        <v>37</v>
+      </c>
+      <c r="F113" s="167"/>
+    </row>
+    <row r="114" spans="1:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="298"/>
+      <c r="B114" s="286"/>
+      <c r="D114" s="77" t="s">
+        <v>346</v>
+      </c>
+      <c r="F114" s="167"/>
+    </row>
+    <row r="115" spans="1:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="298"/>
+      <c r="B115" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="D115" s="77" t="s">
+        <v>345</v>
+      </c>
+      <c r="F115" s="167"/>
+    </row>
+    <row r="116" spans="1:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="153"/>
+      <c r="B116" s="293"/>
+      <c r="D116" s="246" t="s">
+        <v>371</v>
+      </c>
+      <c r="F116" s="238"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="327" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" s="328"/>
+      <c r="C117" s="328"/>
+      <c r="D117" s="328"/>
+      <c r="E117" s="328"/>
+      <c r="F117" s="329"/>
+    </row>
+    <row r="118" spans="1:6" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="332">
+        <v>46186</v>
+      </c>
+      <c r="B118" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="C118" s="160"/>
+      <c r="D118" s="114" t="s">
+        <v>292</v>
+      </c>
+      <c r="E118" s="160"/>
+      <c r="F118" s="176"/>
+    </row>
+    <row r="119" spans="1:6" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="297"/>
+      <c r="B119" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="D119" s="77" t="s">
+        <v>293</v>
+      </c>
+      <c r="F119" s="167"/>
+    </row>
+    <row r="120" spans="1:6" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="333"/>
+      <c r="B120" s="80"/>
+      <c r="C120" s="164"/>
+      <c r="D120" s="222"/>
+      <c r="E120" s="164"/>
+      <c r="F120" s="230"/>
+    </row>
+    <row r="121" spans="1:6" s="10" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="335" t="s">
+        <v>370</v>
+      </c>
+      <c r="B121" s="335"/>
+      <c r="C121" s="335"/>
+      <c r="D121" s="335"/>
+      <c r="E121" s="335"/>
+      <c r="F121" s="335"/>
+    </row>
+    <row r="124" spans="1:6" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="F124" s="68" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="F125" s="68" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="54">
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A83:A87"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="A42:A49"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="A118:A120"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="A96:A100"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="A70:A76"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C28:C34"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="E28:E34"/>
+    <mergeCell ref="A19:A26"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C36:C40"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="A28:A34"/>
+    <mergeCell ref="A5:A10"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C35">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E41">
+    <cfRule type="duplicateValues" dxfId="5" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E41:E49">
+    <cfRule type="duplicateValues" dxfId="4" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E50">
+    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="17" max="16383" man="1"/>
+    <brk id="35" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J216"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="58.5703125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="2.7109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="45.85546875" style="18" customWidth="1"/>
+    <col min="5" max="5" width="2.7109375" style="18" customWidth="1"/>
+    <col min="6" max="6" width="72.85546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="219" customFormat="1" ht="31.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="337" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="338"/>
+      <c r="C1" s="338"/>
+      <c r="D1" s="338"/>
+      <c r="E1" s="338"/>
+      <c r="F1" s="339"/>
+    </row>
+    <row r="2" spans="1:7" s="219" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="340" t="s">
+        <v>275</v>
+      </c>
+      <c r="B2" s="341"/>
+      <c r="C2" s="341"/>
+      <c r="D2" s="341"/>
+      <c r="E2" s="341"/>
+      <c r="F2" s="342"/>
+    </row>
+    <row r="3" spans="1:7" s="219" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="340" t="s">
+        <v>276</v>
+      </c>
+      <c r="B3" s="341"/>
+      <c r="C3" s="341"/>
+      <c r="D3" s="341"/>
+      <c r="E3" s="341"/>
+      <c r="F3" s="342"/>
+      <c r="G3" s="249"/>
+    </row>
+    <row r="4" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="343" t="s">
+        <v>391</v>
+      </c>
+      <c r="B4" s="316"/>
+      <c r="C4" s="316"/>
+      <c r="D4" s="316"/>
+      <c r="E4" s="316"/>
+      <c r="F4" s="221" t="s">
+        <v>389</v>
+      </c>
+      <c r="G4" s="249"/>
+    </row>
+    <row r="5" spans="1:7" ht="60.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="54"/>
+      <c r="D5" s="53" t="s">
+        <v>273</v>
+      </c>
+      <c r="E5" s="225"/>
+      <c r="F5" s="53" t="s">
+        <v>274</v>
+      </c>
+      <c r="G5" s="249"/>
+    </row>
+    <row r="6" spans="1:7" s="12" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="332">
+        <v>46160</v>
+      </c>
+      <c r="B6" s="126" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="145"/>
+      <c r="D6" s="336" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="259"/>
+      <c r="F6" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" s="249"/>
+    </row>
+    <row r="7" spans="1:7" s="12" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="297"/>
+      <c r="B7" s="94" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="85"/>
+      <c r="D7" s="336"/>
+      <c r="E7" s="250"/>
+      <c r="F7" s="92" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="249"/>
+    </row>
+    <row r="8" spans="1:7" s="12" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="297"/>
+      <c r="B8" s="126" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="85"/>
+      <c r="D8" s="257" t="s">
+        <v>367</v>
+      </c>
+      <c r="E8" s="250"/>
+      <c r="F8" s="60" t="s">
+        <v>231</v>
+      </c>
+      <c r="G8" s="249"/>
+    </row>
+    <row r="9" spans="1:7" s="12" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="297"/>
+      <c r="B9" s="126" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="85"/>
+      <c r="D9" s="93" t="s">
+        <v>279</v>
+      </c>
+      <c r="E9" s="250"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="249"/>
+    </row>
+    <row r="10" spans="1:7" s="12" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="297"/>
+      <c r="B10" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="85"/>
+      <c r="D10" s="93" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" s="250"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="249"/>
+    </row>
+    <row r="11" spans="1:7" s="12" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="198"/>
+      <c r="B11" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="250"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="249"/>
+    </row>
+    <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="212"/>
+      <c r="B12" s="202"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="222"/>
+    </row>
+    <row r="13" spans="1:7" s="12" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="297">
+        <v>46161</v>
+      </c>
+      <c r="B13" s="344" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="145"/>
+    </row>
+    <row r="14" spans="1:7" s="12" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="297"/>
+      <c r="B14" s="345"/>
+      <c r="D14" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="85"/>
+    </row>
+    <row r="15" spans="1:7" s="12" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="297"/>
+      <c r="B15" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="85"/>
+      <c r="F15" s="85"/>
+    </row>
+    <row r="16" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="212"/>
+      <c r="B16" s="202"/>
+      <c r="C16" s="202"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="202"/>
+      <c r="F16" s="222"/>
+      <c r="G16" s="249"/>
+    </row>
+    <row r="17" spans="1:7" s="12" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="303">
+        <v>46162</v>
+      </c>
+      <c r="B17" s="123" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="336" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" s="61" t="s">
+        <v>145</v>
+      </c>
+      <c r="G17" s="249"/>
+    </row>
+    <row r="18" spans="1:7" s="12" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="303"/>
+      <c r="B18" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="336"/>
+      <c r="F18" s="92" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="249"/>
+    </row>
+    <row r="19" spans="1:7" s="12" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="303"/>
+      <c r="B19" s="145"/>
+      <c r="D19" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="G19" s="249"/>
+    </row>
+    <row r="20" spans="1:7" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="303"/>
+      <c r="B20" s="85"/>
+      <c r="D20" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="F20" s="85"/>
+      <c r="G20" s="249"/>
+    </row>
+    <row r="21" spans="1:7" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="42"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="206"/>
+      <c r="G21" s="249"/>
+    </row>
+    <row r="22" spans="1:7" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="300">
+        <v>46163</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>269</v>
+      </c>
+      <c r="F22" s="145"/>
+      <c r="G22" s="249"/>
+    </row>
+    <row r="23" spans="1:7" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="301"/>
+      <c r="B23" s="48" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" s="85"/>
+      <c r="G23" s="249"/>
+    </row>
+    <row r="24" spans="1:7" s="12" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="301"/>
+      <c r="B24" s="96" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="85"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="249"/>
+    </row>
+    <row r="25" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="212"/>
+      <c r="B25" s="202"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="222"/>
+      <c r="G25" s="249"/>
+    </row>
+    <row r="26" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="300">
+        <v>46164</v>
+      </c>
+      <c r="B26" s="123" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="336" t="s">
+        <v>282</v>
+      </c>
+      <c r="F26" s="92" t="s">
+        <v>161</v>
+      </c>
+      <c r="G26" s="249"/>
+    </row>
+    <row r="27" spans="1:7" ht="116.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="301"/>
+      <c r="B27" s="123" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="336"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="249"/>
+    </row>
+    <row r="28" spans="1:7" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="301"/>
+      <c r="B28" s="123" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="93" t="s">
+        <v>281</v>
+      </c>
+      <c r="F28" s="109"/>
+      <c r="G28" s="249"/>
+    </row>
+    <row r="29" spans="1:7" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="302"/>
+      <c r="B29" s="222"/>
+      <c r="D29" s="252" t="s">
+        <v>371</v>
+      </c>
+      <c r="F29" s="107"/>
+      <c r="G29" s="249"/>
+    </row>
+    <row r="30" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="212"/>
+      <c r="B30" s="202"/>
+      <c r="C30" s="202"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="202"/>
+      <c r="F30" s="222"/>
+      <c r="G30" s="249"/>
+    </row>
+    <row r="31" spans="1:7" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="300">
+        <v>46165</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" s="106"/>
+      <c r="G31" s="249"/>
+    </row>
+    <row r="32" spans="1:7" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="301"/>
+      <c r="B32" s="48" t="s">
+        <v>233</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" s="109"/>
+      <c r="G32" s="249"/>
+    </row>
+    <row r="33" spans="1:7" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="301"/>
+      <c r="B33" s="106"/>
+      <c r="D33" s="51" t="s">
+        <v>283</v>
+      </c>
+      <c r="F33" s="109"/>
+      <c r="G33" s="249"/>
+    </row>
+    <row r="34" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="212"/>
+      <c r="B34" s="202"/>
+      <c r="C34" s="202"/>
+      <c r="D34" s="202"/>
+      <c r="E34" s="202"/>
+      <c r="F34" s="222"/>
+      <c r="G34" s="249"/>
+    </row>
+    <row r="35" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="301">
+        <v>46174</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="215" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="60" t="s">
+        <v>228</v>
+      </c>
+      <c r="G35" s="249"/>
+    </row>
+    <row r="36" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="301"/>
+      <c r="B36" s="256" t="s">
+        <v>373</v>
+      </c>
+      <c r="D36" s="215" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" s="92" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="249"/>
+    </row>
+    <row r="37" spans="1:7" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="301"/>
+      <c r="B37" s="126" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" s="92" t="s">
+        <v>183</v>
+      </c>
+      <c r="G37" s="249"/>
+    </row>
+    <row r="38" spans="1:7" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="301"/>
+      <c r="B38" s="126" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" s="93" t="s">
+        <v>284</v>
+      </c>
+      <c r="F38" s="167"/>
+      <c r="G38" s="249"/>
+    </row>
+    <row r="39" spans="1:7" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="301"/>
+      <c r="B39" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="D39" s="167"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="249"/>
+    </row>
+    <row r="40" spans="1:7" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="301"/>
+      <c r="B40" s="248" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="109"/>
+      <c r="F40" s="107"/>
+      <c r="G40" s="249"/>
+    </row>
+    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="212"/>
+      <c r="B41" s="202"/>
+      <c r="C41" s="202"/>
+      <c r="D41" s="202"/>
+      <c r="E41" s="202"/>
+      <c r="F41" s="222"/>
+      <c r="G41" s="249"/>
+    </row>
+    <row r="42" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="301">
+        <v>46175</v>
+      </c>
+      <c r="B42" s="346" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" s="127" t="s">
+        <v>121</v>
+      </c>
+      <c r="F42" s="92" t="s">
+        <v>325</v>
+      </c>
+      <c r="G42" s="249"/>
+    </row>
+    <row r="43" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="301"/>
+      <c r="B43" s="347"/>
+      <c r="D43" s="127" t="s">
+        <v>129</v>
+      </c>
+      <c r="F43" s="167"/>
+      <c r="G43" s="249"/>
+    </row>
+    <row r="44" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="301"/>
+      <c r="B44" s="126" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="96" t="s">
+        <v>134</v>
+      </c>
+      <c r="F44" s="109"/>
+      <c r="G44" s="249"/>
+    </row>
+    <row r="45" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="301"/>
+      <c r="B45" s="126" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="126" t="s">
+        <v>171</v>
+      </c>
+      <c r="F45" s="109"/>
+      <c r="G45" s="249"/>
+    </row>
+    <row r="46" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="301"/>
+      <c r="B46" s="87"/>
+      <c r="D46" s="254" t="s">
+        <v>147</v>
+      </c>
+      <c r="F46" s="109"/>
+      <c r="G46" s="249"/>
+    </row>
+    <row r="47" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="301"/>
+      <c r="B47" s="230"/>
+      <c r="D47" s="92" t="s">
+        <v>148</v>
+      </c>
+      <c r="F47" s="107"/>
+      <c r="G47" s="249"/>
+    </row>
+    <row r="48" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="212"/>
+      <c r="B48" s="202"/>
+      <c r="C48" s="202"/>
+      <c r="D48" s="202"/>
+      <c r="E48" s="202"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="249"/>
+    </row>
+    <row r="49" spans="1:10" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="334">
+        <v>46176</v>
+      </c>
+      <c r="B49" s="336" t="s">
+        <v>366</v>
+      </c>
+      <c r="D49" s="348" t="s">
+        <v>365</v>
+      </c>
+      <c r="F49" s="106"/>
+      <c r="G49" s="249"/>
+    </row>
+    <row r="50" spans="1:10" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="299"/>
+      <c r="B50" s="336"/>
+      <c r="D50" s="349"/>
+      <c r="F50" s="109"/>
+      <c r="G50" s="249"/>
+    </row>
+    <row r="51" spans="1:10" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="299"/>
+      <c r="B51" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" s="253" t="s">
+        <v>285</v>
+      </c>
+      <c r="F51" s="109"/>
+      <c r="G51" s="249"/>
+    </row>
+    <row r="52" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="212"/>
+      <c r="B52" s="202"/>
+      <c r="C52" s="202"/>
+      <c r="D52" s="202"/>
+      <c r="E52" s="202"/>
+      <c r="F52" s="222"/>
+      <c r="G52" s="249"/>
+    </row>
+    <row r="53" spans="1:10" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="334">
+        <v>46177</v>
+      </c>
+      <c r="B53" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="D53" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="F53" s="92" t="s">
+        <v>6</v>
+      </c>
+      <c r="G53" s="249"/>
+    </row>
+    <row r="54" spans="1:10" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="299"/>
+      <c r="B54" s="96" t="s">
+        <v>163</v>
+      </c>
+      <c r="D54" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="F54" s="60" t="s">
+        <v>178</v>
+      </c>
+      <c r="G54" s="249"/>
+    </row>
+    <row r="55" spans="1:10" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="299"/>
+      <c r="B55" s="126" t="s">
+        <v>323</v>
+      </c>
+      <c r="D55" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="F55" s="106"/>
+      <c r="G55" s="249"/>
+    </row>
+    <row r="56" spans="1:10" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="153"/>
+      <c r="B56" s="26"/>
+      <c r="D56" s="127" t="s">
+        <v>398</v>
+      </c>
+      <c r="F56" s="106"/>
+      <c r="G56" s="249"/>
+    </row>
+    <row r="57" spans="1:10" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="153"/>
+      <c r="B57" s="117"/>
+      <c r="D57" s="127" t="s">
+        <v>399</v>
+      </c>
+      <c r="F57" s="106"/>
+      <c r="G57" s="249"/>
+    </row>
+    <row r="58" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="212"/>
+      <c r="B58" s="202"/>
+      <c r="C58" s="202"/>
+      <c r="D58" s="202"/>
+      <c r="E58" s="202"/>
+      <c r="F58" s="222"/>
+      <c r="G58" s="249"/>
+    </row>
+    <row r="59" spans="1:10" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="334">
+        <v>46178</v>
+      </c>
+      <c r="B59" s="126" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" s="127" t="s">
+        <v>151</v>
+      </c>
+      <c r="F59" s="106"/>
+      <c r="G59" s="249"/>
+    </row>
+    <row r="60" spans="1:10" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="299"/>
+      <c r="B60" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="D60" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="F60" s="109"/>
+      <c r="G60" s="249"/>
+    </row>
+    <row r="61" spans="1:10" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="299"/>
+      <c r="B61" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="D61" s="127" t="s">
+        <v>174</v>
+      </c>
+      <c r="F61" s="109"/>
+      <c r="G61" s="249"/>
+    </row>
+    <row r="62" spans="1:10" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="299"/>
+      <c r="B62" s="167"/>
+      <c r="D62" s="252" t="s">
+        <v>371</v>
+      </c>
+      <c r="F62" s="109"/>
+      <c r="G62" s="249"/>
+    </row>
+    <row r="63" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="212"/>
+      <c r="B63" s="202"/>
+      <c r="C63" s="202"/>
+      <c r="D63" s="202"/>
+      <c r="E63" s="202"/>
+      <c r="F63" s="222"/>
+      <c r="G63" s="249"/>
+      <c r="H63" s="249"/>
+      <c r="I63" s="249"/>
+      <c r="J63" s="249"/>
+    </row>
+    <row r="64" spans="1:10" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="334">
+        <v>46179</v>
+      </c>
+      <c r="B64" s="126" t="s">
+        <v>139</v>
+      </c>
+      <c r="D64" s="127" t="s">
+        <v>177</v>
+      </c>
+      <c r="F64" s="60" t="s">
+        <v>232</v>
+      </c>
+      <c r="G64" s="249"/>
+      <c r="H64" s="249"/>
+      <c r="I64" s="249"/>
+      <c r="J64" s="249"/>
+    </row>
+    <row r="65" spans="1:10" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="299"/>
+      <c r="B65" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="D65" s="354" t="s">
+        <v>182</v>
+      </c>
+      <c r="F65" s="109"/>
+      <c r="G65" s="249"/>
+      <c r="H65" s="249"/>
+      <c r="I65" s="249"/>
+      <c r="J65" s="249"/>
+    </row>
+    <row r="66" spans="1:10" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="299"/>
+      <c r="B66" s="51" t="s">
+        <v>374</v>
+      </c>
+      <c r="D66" s="345"/>
+      <c r="F66" s="109"/>
+      <c r="G66" s="249"/>
+      <c r="H66" s="249"/>
+      <c r="I66" s="249"/>
+      <c r="J66" s="249"/>
+    </row>
+    <row r="67" spans="1:10" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="299"/>
+      <c r="B67" s="109"/>
+      <c r="D67" s="122" t="s">
+        <v>327</v>
+      </c>
+      <c r="F67" s="167"/>
+      <c r="G67" s="249"/>
+      <c r="H67" s="249"/>
+      <c r="I67" s="249"/>
+      <c r="J67" s="249"/>
+    </row>
+    <row r="68" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="299"/>
+      <c r="B68" s="107"/>
+      <c r="D68" s="222"/>
+      <c r="F68" s="107"/>
+      <c r="G68" s="249"/>
+      <c r="H68" s="249"/>
+      <c r="I68" s="249"/>
+      <c r="J68" s="249"/>
+    </row>
+    <row r="69" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="212"/>
+      <c r="B69" s="202"/>
+      <c r="C69" s="202"/>
+      <c r="D69" s="202"/>
+      <c r="E69" s="202"/>
+      <c r="F69" s="222"/>
+      <c r="G69" s="249"/>
+      <c r="H69" s="249"/>
+      <c r="I69" s="249"/>
+      <c r="J69" s="249"/>
+    </row>
+    <row r="70" spans="1:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="334">
+        <v>46181</v>
+      </c>
+      <c r="B70" s="350" t="s">
+        <v>372</v>
+      </c>
+      <c r="D70" s="126" t="s">
+        <v>158</v>
+      </c>
+      <c r="F70" s="176"/>
+      <c r="G70" s="249"/>
+      <c r="H70" s="249"/>
+      <c r="I70" s="249"/>
+      <c r="J70" s="249"/>
+    </row>
+    <row r="71" spans="1:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="299"/>
+      <c r="B71" s="351"/>
+      <c r="D71" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="F71" s="109"/>
+      <c r="G71" s="249"/>
+      <c r="H71" s="249"/>
+      <c r="I71" s="249"/>
+      <c r="J71" s="249"/>
+    </row>
+    <row r="72" spans="1:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="299"/>
+      <c r="B72" s="88"/>
+      <c r="D72" s="251" t="s">
+        <v>189</v>
+      </c>
+      <c r="F72" s="109"/>
+      <c r="G72" s="249"/>
+      <c r="H72" s="249"/>
+      <c r="I72" s="249"/>
+      <c r="J72" s="249"/>
+    </row>
+    <row r="73" spans="1:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="299"/>
+      <c r="B73" s="167"/>
+      <c r="D73" s="248" t="s">
+        <v>160</v>
+      </c>
+      <c r="F73" s="109"/>
+      <c r="G73" s="249"/>
+      <c r="H73" s="249"/>
+      <c r="I73" s="249"/>
+      <c r="J73" s="249"/>
+    </row>
+    <row r="74" spans="1:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="299"/>
+      <c r="B74" s="107"/>
+      <c r="D74" s="92" t="s">
+        <v>164</v>
+      </c>
+      <c r="F74" s="107"/>
+      <c r="G74" s="249"/>
+      <c r="H74" s="249"/>
+      <c r="I74" s="249"/>
+      <c r="J74" s="249"/>
+    </row>
+    <row r="75" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="212"/>
+      <c r="B75" s="202"/>
+      <c r="C75" s="202"/>
+      <c r="D75" s="202"/>
+      <c r="E75" s="202"/>
+      <c r="F75" s="222"/>
+      <c r="G75" s="249"/>
+      <c r="H75" s="249"/>
+      <c r="I75" s="249"/>
+      <c r="J75" s="249"/>
+    </row>
+    <row r="76" spans="1:10" ht="108" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="298">
+        <v>46182</v>
+      </c>
+      <c r="B76" s="336" t="s">
+        <v>364</v>
+      </c>
+      <c r="D76" s="336" t="s">
+        <v>363</v>
+      </c>
+      <c r="F76" s="106"/>
+      <c r="G76" s="249"/>
+      <c r="H76" s="249"/>
+      <c r="I76" s="249"/>
+      <c r="J76" s="249"/>
+    </row>
+    <row r="77" spans="1:10" ht="108" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="298"/>
+      <c r="B77" s="336"/>
+      <c r="D77" s="336"/>
+      <c r="F77" s="109"/>
+      <c r="G77" s="249"/>
+      <c r="H77" s="249"/>
+      <c r="I77" s="249"/>
+      <c r="J77" s="249"/>
+    </row>
+    <row r="78" spans="1:10" ht="108" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="298"/>
+      <c r="B78" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="D78" s="248" t="s">
+        <v>149</v>
+      </c>
+      <c r="F78" s="109"/>
+      <c r="G78" s="249"/>
+      <c r="H78" s="249"/>
+      <c r="I78" s="249"/>
+      <c r="J78" s="249"/>
+    </row>
+    <row r="79" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="212"/>
+      <c r="B79" s="202"/>
+      <c r="C79" s="202"/>
+      <c r="D79" s="202"/>
+      <c r="E79" s="202"/>
+      <c r="F79" s="222"/>
+      <c r="G79" s="249"/>
+      <c r="H79" s="249"/>
+      <c r="I79" s="249"/>
+      <c r="J79" s="249"/>
+    </row>
+    <row r="80" spans="1:10" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="331">
+        <v>46183</v>
+      </c>
+      <c r="B80" s="248" t="s">
+        <v>195</v>
+      </c>
+      <c r="D80" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="F80" s="176"/>
+      <c r="G80" s="249"/>
+      <c r="H80" s="249"/>
+      <c r="I80" s="249"/>
+      <c r="J80" s="249"/>
+    </row>
+    <row r="81" spans="1:10" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="298"/>
+      <c r="B81" s="244" t="s">
+        <v>326</v>
+      </c>
+      <c r="D81" s="244" t="s">
+        <v>328</v>
+      </c>
+      <c r="F81" s="109"/>
+      <c r="G81" s="249"/>
+      <c r="H81" s="249"/>
+      <c r="I81" s="249"/>
+      <c r="J81" s="249"/>
+    </row>
+    <row r="82" spans="1:10" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="298"/>
+      <c r="B82" s="126" t="s">
+        <v>329</v>
+      </c>
+      <c r="D82" s="109"/>
+      <c r="F82" s="107"/>
+      <c r="G82" s="249"/>
+      <c r="H82" s="249"/>
+      <c r="I82" s="249"/>
+      <c r="J82" s="249"/>
+    </row>
+    <row r="83" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="212"/>
+      <c r="B83" s="144"/>
+      <c r="C83" s="144"/>
+      <c r="D83" s="144"/>
+      <c r="E83" s="144"/>
+      <c r="F83" s="258"/>
+      <c r="G83" s="249"/>
+      <c r="H83" s="249"/>
+      <c r="I83" s="249"/>
+      <c r="J83" s="249"/>
+    </row>
+    <row r="84" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="298">
+        <v>46184</v>
+      </c>
+      <c r="B84" s="353" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" s="106"/>
+      <c r="F84" s="106"/>
+      <c r="G84" s="249"/>
+      <c r="H84" s="249"/>
+      <c r="I84" s="249"/>
+      <c r="J84" s="249"/>
+    </row>
+    <row r="85" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="298"/>
+      <c r="B85" s="353"/>
+      <c r="D85" s="109"/>
+      <c r="F85" s="109"/>
+      <c r="G85" s="249"/>
+      <c r="H85" s="249"/>
+      <c r="I85" s="249"/>
+      <c r="J85" s="249"/>
+    </row>
+    <row r="86" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="298"/>
+      <c r="B86" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="D86" s="109"/>
+      <c r="F86" s="109"/>
+      <c r="G86" s="249"/>
+      <c r="H86" s="249"/>
+      <c r="I86" s="249"/>
+      <c r="J86" s="249"/>
+    </row>
+    <row r="87" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="212"/>
+      <c r="B87" s="202"/>
+      <c r="C87" s="202"/>
+      <c r="D87" s="202"/>
+      <c r="E87" s="202"/>
+      <c r="F87" s="222"/>
+      <c r="G87" s="249"/>
+      <c r="H87" s="249"/>
+      <c r="I87" s="249"/>
+      <c r="J87" s="249"/>
+    </row>
+    <row r="88" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="298">
+        <v>46185</v>
+      </c>
+      <c r="B88" s="234" t="s">
+        <v>191</v>
+      </c>
+      <c r="D88" s="106"/>
+      <c r="F88" s="106"/>
+      <c r="G88" s="249"/>
+      <c r="H88" s="249"/>
+      <c r="I88" s="249"/>
+      <c r="J88" s="249"/>
+    </row>
+    <row r="89" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="298"/>
+      <c r="B89" s="248" t="s">
+        <v>331</v>
+      </c>
+      <c r="D89" s="126" t="s">
+        <v>332</v>
+      </c>
+      <c r="F89" s="109"/>
+      <c r="G89" s="249"/>
+      <c r="H89" s="249"/>
+      <c r="I89" s="249"/>
+      <c r="J89" s="249"/>
+    </row>
+    <row r="90" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="298"/>
+      <c r="B90" s="255" t="s">
+        <v>324</v>
+      </c>
+      <c r="D90" s="252" t="s">
+        <v>371</v>
+      </c>
+      <c r="F90" s="109"/>
+      <c r="G90" s="249"/>
+      <c r="H90" s="249"/>
+      <c r="I90" s="249"/>
+      <c r="J90" s="249"/>
+    </row>
+    <row r="91" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="240"/>
+      <c r="B91" s="144"/>
+      <c r="C91" s="144"/>
+      <c r="D91" s="144"/>
+      <c r="E91" s="144"/>
+      <c r="F91" s="258"/>
+      <c r="G91" s="249"/>
+      <c r="H91" s="249"/>
+      <c r="I91" s="249"/>
+      <c r="J91" s="249"/>
+    </row>
+    <row r="92" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="298">
+        <v>46186</v>
+      </c>
+      <c r="B92" s="48" t="s">
+        <v>333</v>
+      </c>
+      <c r="D92" s="126" t="s">
+        <v>334</v>
+      </c>
+      <c r="F92" s="106"/>
+      <c r="G92" s="249"/>
+      <c r="H92" s="249"/>
+      <c r="I92" s="249"/>
+      <c r="J92" s="249"/>
+    </row>
+    <row r="93" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="298"/>
+      <c r="B93" s="222"/>
+      <c r="D93" s="222"/>
+      <c r="F93" s="107"/>
+      <c r="G93" s="249"/>
+      <c r="H93" s="249"/>
+      <c r="I93" s="249"/>
+      <c r="J93" s="249"/>
+    </row>
+    <row r="94" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="240"/>
+      <c r="B94" s="144"/>
+      <c r="C94" s="144"/>
+      <c r="D94" s="144"/>
+      <c r="E94" s="144"/>
+      <c r="F94" s="241"/>
+      <c r="G94" s="249"/>
+      <c r="H94" s="249"/>
+      <c r="I94" s="249"/>
+      <c r="J94" s="249"/>
+    </row>
+    <row r="95" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="352" t="s">
+        <v>392</v>
+      </c>
+      <c r="B95" s="352"/>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
+      <c r="G95" s="249"/>
+      <c r="H95" s="249"/>
+      <c r="I95" s="249"/>
+      <c r="J95" s="249"/>
+    </row>
+    <row r="96" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G96" s="249"/>
+      <c r="H96" s="249"/>
+      <c r="I96" s="249"/>
+      <c r="J96" s="249"/>
+    </row>
+    <row r="97" spans="6:10" ht="30" x14ac:dyDescent="0.2">
+      <c r="G97" s="249"/>
+      <c r="H97" s="249"/>
+      <c r="I97" s="249"/>
+      <c r="J97" s="249"/>
+    </row>
+    <row r="98" spans="6:10" ht="30" x14ac:dyDescent="0.2">
+      <c r="F98" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="G98" s="249"/>
+      <c r="H98" s="249"/>
+      <c r="I98" s="249"/>
+      <c r="J98" s="249"/>
+    </row>
+    <row r="99" spans="6:10" ht="30" x14ac:dyDescent="0.2">
+      <c r="F99" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="G99" s="249"/>
+      <c r="H99" s="249"/>
+      <c r="I99" s="249"/>
+      <c r="J99" s="249"/>
+    </row>
+    <row r="100" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G100" s="249"/>
+      <c r="H100" s="249"/>
+      <c r="I100" s="249"/>
+      <c r="J100" s="249"/>
+    </row>
+    <row r="101" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G101" s="249"/>
+      <c r="H101" s="249"/>
+      <c r="I101" s="249"/>
+      <c r="J101" s="249"/>
+    </row>
+    <row r="102" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G102" s="249"/>
+      <c r="H102" s="249"/>
+      <c r="I102" s="249"/>
+      <c r="J102" s="249"/>
+    </row>
+    <row r="103" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G103" s="249"/>
+      <c r="H103" s="249"/>
+      <c r="I103" s="249"/>
+      <c r="J103" s="249"/>
+    </row>
+    <row r="104" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G104" s="249"/>
+      <c r="H104" s="249"/>
+      <c r="I104" s="249"/>
+      <c r="J104" s="249"/>
+    </row>
+    <row r="105" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G105" s="249"/>
+      <c r="H105" s="249"/>
+      <c r="I105" s="249"/>
+      <c r="J105" s="249"/>
+    </row>
+    <row r="106" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G106" s="249"/>
+      <c r="H106" s="249"/>
+      <c r="I106" s="249"/>
+      <c r="J106" s="249"/>
+    </row>
+    <row r="107" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G107" s="249"/>
+      <c r="H107" s="249"/>
+      <c r="I107" s="249"/>
+      <c r="J107" s="249"/>
+    </row>
+    <row r="108" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G108" s="249"/>
+      <c r="H108" s="249"/>
+      <c r="I108" s="249"/>
+      <c r="J108" s="249"/>
+    </row>
+    <row r="109" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G109" s="249"/>
+      <c r="H109" s="249"/>
+      <c r="I109" s="249"/>
+      <c r="J109" s="249"/>
+    </row>
+    <row r="110" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G110" s="249"/>
+      <c r="H110" s="249"/>
+      <c r="I110" s="249"/>
+      <c r="J110" s="249"/>
+    </row>
+    <row r="111" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G111" s="249"/>
+      <c r="H111" s="249"/>
+      <c r="I111" s="249"/>
+      <c r="J111" s="249"/>
+    </row>
+    <row r="112" spans="6:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G112" s="249"/>
+      <c r="H112" s="249"/>
+      <c r="I112" s="249"/>
+      <c r="J112" s="249"/>
+    </row>
+    <row r="113" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G113" s="249"/>
+      <c r="H113" s="249"/>
+      <c r="I113" s="249"/>
+      <c r="J113" s="249"/>
+    </row>
+    <row r="114" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G114" s="249"/>
+      <c r="H114" s="249"/>
+      <c r="I114" s="249"/>
+      <c r="J114" s="249"/>
+    </row>
+    <row r="115" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G115" s="249"/>
+      <c r="H115" s="249"/>
+      <c r="I115" s="249"/>
+      <c r="J115" s="249"/>
+    </row>
+    <row r="116" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G116" s="249"/>
+      <c r="H116" s="249"/>
+      <c r="I116" s="249"/>
+      <c r="J116" s="249"/>
+    </row>
+    <row r="117" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G117" s="249"/>
+      <c r="H117" s="249"/>
+      <c r="I117" s="249"/>
+      <c r="J117" s="249"/>
+    </row>
+    <row r="118" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G118" s="249"/>
+      <c r="H118" s="249"/>
+      <c r="I118" s="249"/>
+      <c r="J118" s="249"/>
+    </row>
+    <row r="119" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G119" s="249"/>
+      <c r="H119" s="249"/>
+      <c r="I119" s="249"/>
+      <c r="J119" s="249"/>
+    </row>
+    <row r="120" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G120" s="249"/>
+      <c r="H120" s="249"/>
+      <c r="I120" s="249"/>
+      <c r="J120" s="249"/>
+    </row>
+    <row r="121" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G121" s="249"/>
+      <c r="H121" s="249"/>
+      <c r="I121" s="249"/>
+      <c r="J121" s="249"/>
+    </row>
+    <row r="122" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G122" s="249"/>
+      <c r="H122" s="249"/>
+      <c r="I122" s="249"/>
+      <c r="J122" s="249"/>
+    </row>
+    <row r="123" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G123" s="249"/>
+      <c r="H123" s="249"/>
+      <c r="I123" s="249"/>
+      <c r="J123" s="249"/>
+    </row>
+    <row r="124" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G124" s="249"/>
+      <c r="H124" s="249"/>
+      <c r="I124" s="249"/>
+      <c r="J124" s="249"/>
+    </row>
+    <row r="125" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G125" s="249"/>
+      <c r="H125" s="249"/>
+      <c r="I125" s="249"/>
+      <c r="J125" s="249"/>
+    </row>
+    <row r="126" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G126" s="249"/>
+      <c r="H126" s="249"/>
+      <c r="I126" s="249"/>
+      <c r="J126" s="249"/>
+    </row>
+    <row r="127" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G127" s="249"/>
+      <c r="H127" s="249"/>
+      <c r="I127" s="249"/>
+      <c r="J127" s="249"/>
+    </row>
+    <row r="128" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G128" s="249"/>
+      <c r="H128" s="249"/>
+      <c r="I128" s="249"/>
+      <c r="J128" s="249"/>
+    </row>
+    <row r="129" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G129" s="249"/>
+      <c r="H129" s="249"/>
+      <c r="I129" s="249"/>
+      <c r="J129" s="249"/>
+    </row>
+    <row r="130" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G130" s="249"/>
+      <c r="H130" s="249"/>
+      <c r="I130" s="249"/>
+      <c r="J130" s="249"/>
+    </row>
+    <row r="131" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G131" s="249"/>
+      <c r="H131" s="249"/>
+      <c r="I131" s="249"/>
+      <c r="J131" s="249"/>
+    </row>
+    <row r="132" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G132" s="249"/>
+      <c r="H132" s="249"/>
+      <c r="I132" s="249"/>
+      <c r="J132" s="249"/>
+    </row>
+    <row r="133" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G133" s="249"/>
+      <c r="H133" s="249"/>
+      <c r="I133" s="249"/>
+      <c r="J133" s="249"/>
+    </row>
+    <row r="134" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G134" s="249"/>
+      <c r="H134" s="249"/>
+      <c r="I134" s="249"/>
+      <c r="J134" s="249"/>
+    </row>
+    <row r="135" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G135" s="249"/>
+      <c r="H135" s="249"/>
+      <c r="I135" s="249"/>
+      <c r="J135" s="249"/>
+    </row>
+    <row r="136" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G136" s="249"/>
+      <c r="H136" s="249"/>
+      <c r="I136" s="249"/>
+      <c r="J136" s="249"/>
+    </row>
+    <row r="137" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G137" s="249"/>
+      <c r="H137" s="249"/>
+      <c r="I137" s="249"/>
+      <c r="J137" s="249"/>
+    </row>
+    <row r="138" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G138" s="249"/>
+      <c r="H138" s="249"/>
+      <c r="I138" s="249"/>
+      <c r="J138" s="249"/>
+    </row>
+    <row r="139" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G139" s="249"/>
+      <c r="H139" s="249"/>
+      <c r="I139" s="249"/>
+      <c r="J139" s="249"/>
+    </row>
+    <row r="140" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G140" s="249"/>
+      <c r="H140" s="249"/>
+      <c r="I140" s="249"/>
+      <c r="J140" s="249"/>
+    </row>
+    <row r="141" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G141" s="249"/>
+      <c r="H141" s="249"/>
+      <c r="I141" s="249"/>
+      <c r="J141" s="249"/>
+    </row>
+    <row r="142" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G142" s="249"/>
+      <c r="H142" s="249"/>
+      <c r="I142" s="249"/>
+      <c r="J142" s="249"/>
+    </row>
+    <row r="143" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G143" s="249"/>
+      <c r="H143" s="249"/>
+      <c r="I143" s="249"/>
+      <c r="J143" s="249"/>
+    </row>
+    <row r="144" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G144" s="249"/>
+      <c r="H144" s="249"/>
+      <c r="I144" s="249"/>
+      <c r="J144" s="249"/>
+    </row>
+    <row r="145" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G145" s="249"/>
+      <c r="H145" s="249"/>
+      <c r="I145" s="249"/>
+      <c r="J145" s="249"/>
+    </row>
+    <row r="146" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G146" s="249"/>
+      <c r="H146" s="249"/>
+      <c r="I146" s="249"/>
+      <c r="J146" s="249"/>
+    </row>
+    <row r="147" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G147" s="249"/>
+      <c r="H147" s="249"/>
+      <c r="I147" s="249"/>
+      <c r="J147" s="249"/>
+    </row>
+    <row r="148" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G148" s="249"/>
+      <c r="H148" s="249"/>
+      <c r="I148" s="249"/>
+      <c r="J148" s="249"/>
+    </row>
+    <row r="149" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G149" s="249"/>
+      <c r="H149" s="249"/>
+      <c r="I149" s="249"/>
+      <c r="J149" s="249"/>
+    </row>
+    <row r="150" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G150" s="249"/>
+      <c r="H150" s="249"/>
+      <c r="I150" s="249"/>
+      <c r="J150" s="249"/>
+    </row>
+    <row r="151" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G151" s="249"/>
+      <c r="H151" s="249"/>
+      <c r="I151" s="249"/>
+      <c r="J151" s="249"/>
+    </row>
+    <row r="152" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G152" s="249"/>
+      <c r="H152" s="249"/>
+      <c r="I152" s="249"/>
+      <c r="J152" s="249"/>
+    </row>
+    <row r="153" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G153" s="249"/>
+      <c r="H153" s="249"/>
+      <c r="I153" s="249"/>
+      <c r="J153" s="249"/>
+    </row>
+    <row r="154" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G154" s="249"/>
+      <c r="H154" s="249"/>
+      <c r="I154" s="249"/>
+      <c r="J154" s="249"/>
+    </row>
+    <row r="155" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G155" s="249"/>
+      <c r="H155" s="249"/>
+      <c r="I155" s="249"/>
+      <c r="J155" s="249"/>
+    </row>
+    <row r="156" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G156" s="249"/>
+      <c r="H156" s="249"/>
+      <c r="I156" s="249"/>
+      <c r="J156" s="249"/>
+    </row>
+    <row r="157" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G157" s="249"/>
+      <c r="H157" s="249"/>
+      <c r="I157" s="249"/>
+      <c r="J157" s="249"/>
+    </row>
+    <row r="158" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G158" s="249"/>
+      <c r="H158" s="249"/>
+      <c r="I158" s="249"/>
+      <c r="J158" s="249"/>
+    </row>
+    <row r="159" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G159" s="249"/>
+      <c r="H159" s="249"/>
+      <c r="I159" s="249"/>
+      <c r="J159" s="249"/>
+    </row>
+    <row r="160" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G160" s="249"/>
+      <c r="H160" s="249"/>
+      <c r="I160" s="249"/>
+      <c r="J160" s="249"/>
+    </row>
+    <row r="161" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G161" s="249"/>
+      <c r="H161" s="249"/>
+      <c r="I161" s="249"/>
+      <c r="J161" s="249"/>
+    </row>
+    <row r="162" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G162" s="249"/>
+      <c r="H162" s="249"/>
+      <c r="I162" s="249"/>
+      <c r="J162" s="249"/>
+    </row>
+    <row r="163" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G163" s="249"/>
+      <c r="H163" s="249"/>
+      <c r="I163" s="249"/>
+      <c r="J163" s="249"/>
+    </row>
+    <row r="164" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G164" s="249"/>
+      <c r="H164" s="249"/>
+      <c r="I164" s="249"/>
+      <c r="J164" s="249"/>
+    </row>
+    <row r="165" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G165" s="249"/>
+      <c r="H165" s="249"/>
+      <c r="I165" s="249"/>
+      <c r="J165" s="249"/>
+    </row>
+    <row r="166" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G166" s="249"/>
+      <c r="H166" s="249"/>
+      <c r="I166" s="249"/>
+      <c r="J166" s="249"/>
+    </row>
+    <row r="167" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G167" s="249"/>
+      <c r="H167" s="249"/>
+      <c r="I167" s="249"/>
+      <c r="J167" s="249"/>
+    </row>
+    <row r="168" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G168" s="249"/>
+      <c r="H168" s="249"/>
+      <c r="I168" s="249"/>
+      <c r="J168" s="249"/>
+    </row>
+    <row r="169" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G169" s="249"/>
+      <c r="H169" s="249"/>
+      <c r="I169" s="249"/>
+      <c r="J169" s="249"/>
+    </row>
+    <row r="170" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G170" s="249"/>
+      <c r="H170" s="249"/>
+      <c r="I170" s="249"/>
+      <c r="J170" s="249"/>
+    </row>
+    <row r="171" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G171" s="249"/>
+      <c r="H171" s="249"/>
+      <c r="I171" s="249"/>
+      <c r="J171" s="249"/>
+    </row>
+    <row r="172" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G172" s="249"/>
+      <c r="H172" s="249"/>
+      <c r="I172" s="249"/>
+      <c r="J172" s="249"/>
+    </row>
+    <row r="173" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G173" s="249"/>
+      <c r="H173" s="249"/>
+      <c r="I173" s="249"/>
+      <c r="J173" s="249"/>
+    </row>
+    <row r="174" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G174" s="249"/>
+      <c r="H174" s="249"/>
+      <c r="I174" s="249"/>
+      <c r="J174" s="249"/>
+    </row>
+    <row r="175" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G175" s="249"/>
+      <c r="H175" s="249"/>
+      <c r="I175" s="249"/>
+      <c r="J175" s="249"/>
+    </row>
+    <row r="176" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G176" s="249"/>
+      <c r="H176" s="249"/>
+      <c r="I176" s="249"/>
+      <c r="J176" s="249"/>
+    </row>
+    <row r="177" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G177" s="249"/>
+      <c r="H177" s="249"/>
+      <c r="I177" s="249"/>
+      <c r="J177" s="249"/>
+    </row>
+    <row r="178" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G178" s="249"/>
+      <c r="H178" s="249"/>
+      <c r="I178" s="249"/>
+      <c r="J178" s="249"/>
+    </row>
+    <row r="179" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G179" s="249"/>
+      <c r="H179" s="249"/>
+      <c r="I179" s="249"/>
+      <c r="J179" s="249"/>
+    </row>
+    <row r="180" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G180" s="249"/>
+      <c r="H180" s="249"/>
+      <c r="I180" s="249"/>
+      <c r="J180" s="249"/>
+    </row>
+    <row r="181" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G181" s="249"/>
+      <c r="H181" s="249"/>
+      <c r="I181" s="249"/>
+      <c r="J181" s="249"/>
+    </row>
+    <row r="182" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G182" s="249"/>
+      <c r="H182" s="249"/>
+      <c r="I182" s="249"/>
+      <c r="J182" s="249"/>
+    </row>
+    <row r="183" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G183" s="249"/>
+      <c r="H183" s="249"/>
+      <c r="I183" s="249"/>
+      <c r="J183" s="249"/>
+    </row>
+    <row r="184" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G184" s="249"/>
+      <c r="H184" s="249"/>
+      <c r="I184" s="249"/>
+      <c r="J184" s="249"/>
+    </row>
+    <row r="185" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G185" s="249"/>
+      <c r="H185" s="249"/>
+      <c r="I185" s="249"/>
+      <c r="J185" s="249"/>
+    </row>
+    <row r="186" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G186" s="249"/>
+      <c r="H186" s="249"/>
+      <c r="I186" s="249"/>
+      <c r="J186" s="249"/>
+    </row>
+    <row r="187" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G187" s="249"/>
+      <c r="H187" s="249"/>
+      <c r="I187" s="249"/>
+      <c r="J187" s="249"/>
+    </row>
+    <row r="188" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G188" s="249"/>
+      <c r="H188" s="249"/>
+      <c r="I188" s="249"/>
+      <c r="J188" s="249"/>
+    </row>
+    <row r="189" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G189" s="249"/>
+      <c r="H189" s="249"/>
+      <c r="I189" s="249"/>
+      <c r="J189" s="249"/>
+    </row>
+    <row r="190" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G190" s="249"/>
+      <c r="H190" s="249"/>
+      <c r="I190" s="249"/>
+      <c r="J190" s="249"/>
+    </row>
+    <row r="191" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G191" s="249"/>
+      <c r="H191" s="249"/>
+      <c r="I191" s="249"/>
+      <c r="J191" s="249"/>
+    </row>
+    <row r="192" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G192" s="249"/>
+      <c r="H192" s="249"/>
+      <c r="I192" s="249"/>
+      <c r="J192" s="249"/>
+    </row>
+    <row r="193" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G193" s="249"/>
+      <c r="H193" s="249"/>
+      <c r="I193" s="249"/>
+      <c r="J193" s="249"/>
+    </row>
+    <row r="194" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G194" s="249"/>
+      <c r="H194" s="249"/>
+      <c r="I194" s="249"/>
+      <c r="J194" s="249"/>
+    </row>
+    <row r="195" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G195" s="249"/>
+      <c r="H195" s="249"/>
+      <c r="I195" s="249"/>
+      <c r="J195" s="249"/>
+    </row>
+    <row r="196" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G196" s="249"/>
+      <c r="H196" s="249"/>
+      <c r="I196" s="249"/>
+      <c r="J196" s="249"/>
+    </row>
+    <row r="197" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G197" s="249"/>
+      <c r="H197" s="249"/>
+      <c r="I197" s="249"/>
+      <c r="J197" s="249"/>
+    </row>
+    <row r="198" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G198" s="249"/>
+      <c r="H198" s="249"/>
+      <c r="I198" s="249"/>
+      <c r="J198" s="249"/>
+    </row>
+    <row r="199" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G199" s="249"/>
+      <c r="H199" s="249"/>
+      <c r="I199" s="249"/>
+      <c r="J199" s="249"/>
+    </row>
+    <row r="200" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G200" s="249"/>
+      <c r="H200" s="249"/>
+      <c r="I200" s="249"/>
+      <c r="J200" s="249"/>
+    </row>
+    <row r="201" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G201" s="249"/>
+      <c r="H201" s="249"/>
+      <c r="I201" s="249"/>
+      <c r="J201" s="249"/>
+    </row>
+    <row r="202" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G202" s="249"/>
+      <c r="H202" s="249"/>
+      <c r="I202" s="249"/>
+      <c r="J202" s="249"/>
+    </row>
+    <row r="203" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G203" s="249"/>
+      <c r="H203" s="249"/>
+      <c r="I203" s="249"/>
+      <c r="J203" s="249"/>
+    </row>
+    <row r="204" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G204" s="249"/>
+      <c r="H204" s="249"/>
+      <c r="I204" s="249"/>
+      <c r="J204" s="249"/>
+    </row>
+    <row r="205" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G205" s="249"/>
+      <c r="H205" s="249"/>
+      <c r="I205" s="249"/>
+      <c r="J205" s="249"/>
+    </row>
+    <row r="206" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G206" s="249"/>
+      <c r="H206" s="249"/>
+      <c r="I206" s="249"/>
+      <c r="J206" s="249"/>
+    </row>
+    <row r="207" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G207" s="249"/>
+      <c r="H207" s="249"/>
+      <c r="I207" s="249"/>
+      <c r="J207" s="249"/>
+    </row>
+    <row r="208" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G208" s="249"/>
+      <c r="H208" s="249"/>
+      <c r="I208" s="249"/>
+      <c r="J208" s="249"/>
+    </row>
+    <row r="209" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G209" s="249"/>
+      <c r="H209" s="249"/>
+      <c r="I209" s="249"/>
+      <c r="J209" s="249"/>
+    </row>
+    <row r="210" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G210" s="249"/>
+      <c r="H210" s="249"/>
+      <c r="I210" s="249"/>
+      <c r="J210" s="249"/>
+    </row>
+    <row r="211" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G211" s="249"/>
+      <c r="H211" s="249"/>
+      <c r="I211" s="249"/>
+      <c r="J211" s="249"/>
+    </row>
+    <row r="212" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G212" s="249"/>
+      <c r="H212" s="249"/>
+      <c r="I212" s="249"/>
+      <c r="J212" s="249"/>
+    </row>
+    <row r="213" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G213" s="249"/>
+      <c r="H213" s="249"/>
+      <c r="I213" s="249"/>
+      <c r="J213" s="249"/>
+    </row>
+    <row r="214" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G214" s="249"/>
+      <c r="H214" s="249"/>
+      <c r="I214" s="249"/>
+      <c r="J214" s="249"/>
+    </row>
+    <row r="215" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G215" s="249"/>
+      <c r="H215" s="249"/>
+      <c r="I215" s="249"/>
+      <c r="J215" s="249"/>
+    </row>
+    <row r="216" spans="7:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G216" s="249"/>
+      <c r="H216" s="249"/>
+      <c r="I216" s="249"/>
+      <c r="J216" s="249"/>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A64:A68"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="A88:A90"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="A70:A74"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A17:A20"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.45" right="0.2" top="0" bottom="0" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="44" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="17" max="15" man="1"/>
+    <brk id="29" max="5" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="9" customWidth="1"/>
@@ -5455,59 +9918,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="25" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="363" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="240"/>
-      <c r="C1" s="240"/>
-      <c r="D1" s="240"/>
-      <c r="E1" s="240"/>
-      <c r="F1" s="240"/>
-      <c r="G1" s="240"/>
-      <c r="H1" s="240"/>
-      <c r="I1" s="240"/>
-      <c r="J1" s="240"/>
-      <c r="K1" s="240"/>
-      <c r="L1" s="240"/>
-      <c r="M1" s="240"/>
-      <c r="N1" s="240"/>
+      <c r="B1" s="363"/>
+      <c r="C1" s="363"/>
+      <c r="D1" s="363"/>
+      <c r="E1" s="363"/>
+      <c r="F1" s="363"/>
+      <c r="G1" s="363"/>
+      <c r="H1" s="363"/>
+      <c r="I1" s="363"/>
+      <c r="J1" s="363"/>
+      <c r="K1" s="363"/>
+      <c r="L1" s="363"/>
+      <c r="M1" s="363"/>
+      <c r="N1" s="363"/>
     </row>
     <row r="2" spans="1:16" s="25" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="245" t="s">
-        <v>269</v>
-      </c>
-      <c r="B2" s="245"/>
-      <c r="C2" s="245"/>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="245"/>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
-      <c r="M2" s="245"/>
-      <c r="N2" s="245"/>
+      <c r="A2" s="365" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="365"/>
+      <c r="C2" s="365"/>
+      <c r="D2" s="365"/>
+      <c r="E2" s="365"/>
+      <c r="F2" s="365"/>
+      <c r="G2" s="365"/>
+      <c r="H2" s="365"/>
+      <c r="I2" s="365"/>
+      <c r="J2" s="365"/>
+      <c r="K2" s="365"/>
+      <c r="L2" s="365"/>
+      <c r="M2" s="365"/>
+      <c r="N2" s="365"/>
     </row>
     <row r="3" spans="1:16" s="25" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="241" t="s">
-        <v>266</v>
-      </c>
-      <c r="B3" s="241"/>
-      <c r="C3" s="241"/>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="241"/>
-      <c r="I3" s="241"/>
-      <c r="J3" s="241"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="241"/>
+      <c r="A3" s="364" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
+      <c r="L3" s="364"/>
       <c r="M3" s="91"/>
       <c r="P3" s="46" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5543,18 +10006,18 @@
       </c>
       <c r="O4" s="144"/>
       <c r="P4" s="53" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="242">
-        <v>46125</v>
-      </c>
-      <c r="B5" s="248" t="s">
+      <c r="A5" s="358">
+        <v>46121</v>
+      </c>
+      <c r="B5" s="346" t="s">
         <v>117</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="246" t="s">
+      <c r="D5" s="354" t="s">
         <v>118</v>
       </c>
       <c r="E5" s="55"/>
@@ -5581,16 +10044,16 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="243"/>
-      <c r="B6" s="249"/>
+      <c r="A6" s="359"/>
+      <c r="B6" s="366"/>
       <c r="C6" s="23"/>
-      <c r="D6" s="247"/>
+      <c r="D6" s="344"/>
       <c r="E6" s="27"/>
       <c r="F6" s="51" t="s">
         <v>124</v>
       </c>
       <c r="G6" s="27"/>
-      <c r="H6" s="251" t="s">
+      <c r="H6" s="367" t="s">
         <v>120</v>
       </c>
       <c r="I6" s="19"/>
@@ -5608,15 +10071,15 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="243"/>
-      <c r="B7" s="250"/>
+      <c r="A7" s="359"/>
+      <c r="B7" s="347"/>
       <c r="C7" s="23"/>
       <c r="D7" s="48" t="s">
         <v>126</v>
       </c>
       <c r="E7" s="27"/>
       <c r="G7" s="27"/>
-      <c r="H7" s="252"/>
+      <c r="H7" s="368"/>
       <c r="I7" s="24"/>
       <c r="J7" s="96" t="s">
         <v>134</v>
@@ -5632,13 +10095,13 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="244"/>
+      <c r="A8" s="360"/>
       <c r="B8" s="51" t="s">
         <v>132</v>
       </c>
       <c r="C8" s="162"/>
       <c r="D8" s="93" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="E8" s="163"/>
       <c r="F8" s="164"/>
@@ -5652,7 +10115,7 @@
       </c>
       <c r="K8" s="162"/>
       <c r="L8" s="127" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="M8" s="117"/>
       <c r="N8" s="107"/>
@@ -5675,338 +10138,363 @@
       <c r="M9" s="169"/>
       <c r="N9" s="159"/>
     </row>
-    <row r="10" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="242">
-        <v>46126</v>
-      </c>
-      <c r="B10" s="248" t="s">
+    <row r="10" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="E10" s="54"/>
+      <c r="F10" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="J10" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="K10" s="89"/>
+      <c r="L10" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="M10" s="45"/>
+      <c r="N10" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="O10" s="144"/>
+      <c r="P10" s="53" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="358">
+        <v>46122</v>
+      </c>
+      <c r="B11" s="346" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="127" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="127" t="s">
         <v>175</v>
       </c>
-      <c r="E10" s="55"/>
-      <c r="F10" s="253" t="s">
+      <c r="E11" s="55"/>
+      <c r="F11" s="350" t="s">
         <v>140</v>
       </c>
-      <c r="G10" s="55"/>
-      <c r="H10" s="194"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="123" t="s">
+      <c r="G11" s="55"/>
+      <c r="H11" s="313" t="s">
+        <v>240</v>
+      </c>
+      <c r="I11" s="87"/>
+      <c r="J11" s="123" t="s">
         <v>142</v>
       </c>
-      <c r="K10" s="160"/>
-      <c r="L10" s="122" t="s">
+      <c r="K11" s="160"/>
+      <c r="L11" s="122" t="s">
         <v>143</v>
       </c>
-      <c r="M10" s="26"/>
-      <c r="N10" s="122" t="s">
+      <c r="M11" s="26"/>
+      <c r="N11" s="122" t="s">
         <v>176</v>
       </c>
-      <c r="O10" s="161"/>
-      <c r="P10" s="60" t="s">
+      <c r="O11" s="161"/>
+      <c r="P11" s="60" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="243"/>
-      <c r="B11" s="250"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="126" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="256"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="123" t="s">
-        <v>152</v>
-      </c>
-      <c r="L11" s="106"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="124" t="s">
-        <v>147</v>
-      </c>
-      <c r="P11" s="92" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="243"/>
-      <c r="B12" s="248" t="s">
-        <v>141</v>
-      </c>
+    <row r="12" spans="1:16" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="359"/>
+      <c r="B12" s="347"/>
       <c r="C12" s="23"/>
       <c r="D12" s="126" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E12" s="27"/>
-      <c r="F12" s="124" t="s">
-        <v>261</v>
-      </c>
+      <c r="F12" s="355"/>
       <c r="G12" s="27"/>
-      <c r="H12" s="195"/>
+      <c r="H12" s="314"/>
       <c r="I12" s="88"/>
       <c r="J12" s="123" t="s">
+        <v>152</v>
+      </c>
+      <c r="L12" s="106"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="124" t="s">
+        <v>147</v>
+      </c>
+      <c r="P12" s="92" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="359"/>
+      <c r="B13" s="346" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="126" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="27"/>
+      <c r="F13" s="124" t="s">
+        <v>268</v>
+      </c>
+      <c r="G13" s="27"/>
+      <c r="H13" s="314"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="123" t="s">
         <v>154</v>
-      </c>
-      <c r="L12" s="109"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="126" t="s">
-        <v>171</v>
-      </c>
-      <c r="P12" s="61" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="243"/>
-      <c r="B13" s="249"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="93" t="s">
-        <v>255</v>
-      </c>
-      <c r="E13" s="27"/>
-      <c r="F13" s="48" t="s">
-        <v>186</v>
-      </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="195"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="127" t="s">
-        <v>151</v>
       </c>
       <c r="L13" s="109"/>
       <c r="M13" s="14"/>
-      <c r="N13" s="92" t="s">
+      <c r="N13" s="126" t="s">
+        <v>171</v>
+      </c>
+      <c r="P13" s="61" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="359"/>
+      <c r="B14" s="366"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="93" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="314"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="127" t="s">
+        <v>151</v>
+      </c>
+      <c r="L14" s="109"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="92" t="s">
         <v>148</v>
       </c>
-      <c r="P13" s="108"/>
-    </row>
-    <row r="14" spans="1:16" ht="160.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="244"/>
-      <c r="B14" s="51" t="s">
+      <c r="P14" s="108"/>
+    </row>
+    <row r="15" spans="1:16" ht="160.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="360"/>
+      <c r="B15" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="162"/>
-      <c r="D14" s="93" t="s">
-        <v>256</v>
-      </c>
-      <c r="E14" s="163"/>
-      <c r="F14" s="48" t="s">
+      <c r="C15" s="162"/>
+      <c r="D15" s="93" t="s">
+        <v>263</v>
+      </c>
+      <c r="E15" s="163"/>
+      <c r="F15" s="48" t="s">
         <v>233</v>
       </c>
-      <c r="G14" s="163"/>
-      <c r="H14" s="196"/>
-      <c r="I14" s="143"/>
-      <c r="J14" s="51" t="s">
+      <c r="G15" s="163"/>
+      <c r="H15" s="369"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="K14" s="164"/>
-      <c r="L14" s="107"/>
-      <c r="M14" s="117"/>
-      <c r="N14" s="60" t="s">
+      <c r="K15" s="164"/>
+      <c r="L15" s="107"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="60" t="s">
         <v>232</v>
       </c>
-      <c r="O14" s="166"/>
-      <c r="P14" s="105"/>
-    </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="191"/>
-      <c r="B15" s="192"/>
-      <c r="C15" s="192"/>
-      <c r="D15" s="192"/>
-      <c r="E15" s="192"/>
-      <c r="F15" s="192"/>
-      <c r="G15" s="192"/>
-      <c r="H15" s="192"/>
-      <c r="I15" s="192"/>
-      <c r="J15" s="192"/>
-      <c r="K15" s="192"/>
-      <c r="L15" s="192"/>
-      <c r="M15" s="192"/>
-      <c r="N15" s="192"/>
-      <c r="O15" s="192"/>
-      <c r="P15" s="193"/>
-    </row>
-    <row r="16" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="39" t="s">
+      <c r="O15" s="166"/>
+      <c r="P15" s="105"/>
+    </row>
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="191"/>
+      <c r="B16" s="192"/>
+      <c r="C16" s="192"/>
+      <c r="D16" s="192"/>
+      <c r="E16" s="192"/>
+      <c r="F16" s="192"/>
+      <c r="G16" s="192"/>
+      <c r="H16" s="192"/>
+      <c r="I16" s="192"/>
+      <c r="J16" s="192"/>
+      <c r="K16" s="192"/>
+      <c r="L16" s="192"/>
+      <c r="M16" s="192"/>
+      <c r="N16" s="192"/>
+      <c r="O16" s="192"/>
+      <c r="P16" s="193"/>
+    </row>
+    <row r="17" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B17" s="53" t="s">
         <v>234</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="53" t="s">
+      <c r="C17" s="54"/>
+      <c r="D17" s="53" t="s">
         <v>235</v>
       </c>
-      <c r="E16" s="54"/>
-      <c r="F16" s="53" t="s">
+      <c r="E17" s="54"/>
+      <c r="F17" s="53" t="s">
         <v>236</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="53" t="s">
+      <c r="G17" s="4"/>
+      <c r="H17" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="53" t="s">
+      <c r="I17" s="45"/>
+      <c r="J17" s="53" t="s">
         <v>237</v>
       </c>
-      <c r="K16" s="89"/>
-      <c r="L16" s="53" t="s">
+      <c r="K17" s="89"/>
+      <c r="L17" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="M16" s="45"/>
-      <c r="N16" s="53" t="s">
+      <c r="M17" s="45"/>
+      <c r="N17" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="O16" s="144"/>
-      <c r="P16" s="53" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="242">
-        <v>46127</v>
-      </c>
-      <c r="B17" s="260" t="s">
+      <c r="O17" s="144"/>
+      <c r="P17" s="53" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="358">
+        <v>46123</v>
+      </c>
+      <c r="B18" s="336" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="51" t="s">
+      <c r="C18" s="26"/>
+      <c r="D18" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="E17" s="87"/>
-      <c r="F17" s="125" t="s">
+      <c r="E18" s="87"/>
+      <c r="F18" s="125" t="s">
         <v>189</v>
       </c>
-      <c r="G17" s="87"/>
-      <c r="H17" s="51" t="s">
+      <c r="G18" s="87"/>
+      <c r="H18" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="I17" s="118"/>
-      <c r="J17" s="48" t="s">
+      <c r="I18" s="118"/>
+      <c r="J18" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="253" t="s">
+      <c r="K18" s="26"/>
+      <c r="L18" s="350" t="s">
         <v>159</v>
       </c>
-      <c r="M17" s="28"/>
-      <c r="N17" s="92" t="s">
+      <c r="M18" s="28"/>
+      <c r="N18" s="92" t="s">
         <v>164</v>
       </c>
-      <c r="O17" s="161"/>
-      <c r="P17" s="92" t="s">
+      <c r="O18" s="161"/>
+      <c r="P18" s="92" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="243"/>
-      <c r="B18" s="260"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="126" t="s">
+    <row r="19" spans="1:16" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="359"/>
+      <c r="B19" s="336"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="126" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="88"/>
-      <c r="F18" s="126" t="s">
+      <c r="E19" s="88"/>
+      <c r="F19" s="126" t="s">
         <v>158</v>
       </c>
-      <c r="G18" s="88"/>
-      <c r="H18" s="124" t="s">
+      <c r="G19" s="88"/>
+      <c r="H19" s="124" t="s">
         <v>194</v>
       </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="126" t="s">
+      <c r="I19" s="19"/>
+      <c r="J19" s="126" t="s">
         <v>169</v>
       </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="256"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="126" t="s">
+      <c r="K19" s="14"/>
+      <c r="L19" s="355"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="126" t="s">
         <v>135</v>
       </c>
-      <c r="P18" s="60" t="s">
+      <c r="P19" s="60" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="243"/>
-      <c r="B19" s="126" t="s">
+    <row r="20" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="359"/>
+      <c r="B20" s="126" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="E19" s="88"/>
-      <c r="F19" s="48" t="s">
+      <c r="C20" s="23"/>
+      <c r="D20" s="51" t="s">
+        <v>246</v>
+      </c>
+      <c r="E20" s="88"/>
+      <c r="F20" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="88"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="48" t="s">
+      <c r="G20" s="88"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="51" t="s">
+      <c r="K20" s="14"/>
+      <c r="L20" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="M19" s="24"/>
-      <c r="N19" s="106"/>
-      <c r="P19" s="108"/>
-    </row>
-    <row r="20" spans="1:16" s="50" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="243"/>
-      <c r="B20" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="C20" s="49"/>
-      <c r="D20" s="248" t="s">
-        <v>241</v>
-      </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="51" t="s">
+      <c r="M20" s="24"/>
+      <c r="N20" s="106"/>
+      <c r="P20" s="108"/>
+    </row>
+    <row r="21" spans="1:16" s="50" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="359"/>
+      <c r="B21" s="51" t="s">
+        <v>269</v>
+      </c>
+      <c r="C21" s="49"/>
+      <c r="D21" s="346" t="s">
+        <v>247</v>
+      </c>
+      <c r="E21" s="88"/>
+      <c r="F21" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="G20" s="88"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="93" t="s">
-        <v>258</v>
-      </c>
-      <c r="K20" s="88"/>
-      <c r="L20" s="124" t="s">
+      <c r="G21" s="88"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="93" t="s">
+        <v>265</v>
+      </c>
+      <c r="K21" s="88"/>
+      <c r="L21" s="124" t="s">
         <v>170</v>
       </c>
-      <c r="M20" s="24"/>
-      <c r="N20" s="109"/>
-      <c r="P20" s="170"/>
-    </row>
-    <row r="21" spans="1:16" s="50" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="243"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="250"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="197" t="s">
-        <v>251</v>
-      </c>
-      <c r="G21" s="88"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="142"/>
-      <c r="K21" s="88"/>
       <c r="M21" s="24"/>
       <c r="N21" s="109"/>
       <c r="P21" s="170"/>
     </row>
     <row r="22" spans="1:16" s="50" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="243"/>
+      <c r="A22" s="359"/>
       <c r="C22" s="49"/>
+      <c r="D22" s="347"/>
       <c r="E22" s="88"/>
-      <c r="F22" s="198"/>
+      <c r="F22" s="273" t="s">
+        <v>257</v>
+      </c>
       <c r="G22" s="88"/>
       <c r="I22" s="19"/>
       <c r="J22" s="142"/>
@@ -6015,309 +10503,328 @@
       <c r="N22" s="109"/>
       <c r="P22" s="170"/>
     </row>
-    <row r="23" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="188"/>
-      <c r="B23" s="189"/>
-      <c r="C23" s="189"/>
-      <c r="D23" s="189"/>
-      <c r="E23" s="189"/>
-      <c r="F23" s="189"/>
-      <c r="G23" s="189"/>
-      <c r="H23" s="189"/>
-      <c r="I23" s="189"/>
-      <c r="J23" s="189"/>
-      <c r="K23" s="189"/>
-      <c r="L23" s="189"/>
-      <c r="M23" s="189"/>
-      <c r="N23" s="190"/>
-      <c r="O23" s="161"/>
-      <c r="P23" s="141"/>
-    </row>
-    <row r="24" spans="1:16" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="242">
-        <v>46128</v>
-      </c>
-      <c r="B24" s="127" t="s">
+    <row r="23" spans="1:16" s="50" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="359"/>
+      <c r="C23" s="49"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="295"/>
+      <c r="G23" s="88"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="88"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="109"/>
+      <c r="P23" s="170"/>
+    </row>
+    <row r="24" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="188"/>
+      <c r="B24" s="189"/>
+      <c r="C24" s="189"/>
+      <c r="D24" s="189"/>
+      <c r="E24" s="189"/>
+      <c r="F24" s="189"/>
+      <c r="G24" s="189"/>
+      <c r="H24" s="189"/>
+      <c r="I24" s="189"/>
+      <c r="J24" s="189"/>
+      <c r="K24" s="189"/>
+      <c r="L24" s="189"/>
+      <c r="M24" s="189"/>
+      <c r="N24" s="190"/>
+      <c r="O24" s="161"/>
+      <c r="P24" s="141"/>
+    </row>
+    <row r="25" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="54"/>
+      <c r="D25" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25" s="54"/>
+      <c r="F25" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="45"/>
+      <c r="J25" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="K25" s="89"/>
+      <c r="L25" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="M25" s="45"/>
+      <c r="N25" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="O25" s="144"/>
+      <c r="P25" s="53" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="358">
+        <v>46125</v>
+      </c>
+      <c r="B26" s="127" t="s">
         <v>173</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="48" t="s">
+      <c r="C26" s="26"/>
+      <c r="D26" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="E24" s="87"/>
-      <c r="F24" s="126" t="s">
+      <c r="E26" s="87"/>
+      <c r="F26" s="126" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="87"/>
-      <c r="H24" s="48" t="s">
+      <c r="G26" s="87"/>
+      <c r="H26" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="I24" s="95"/>
-      <c r="J24" s="127" t="s">
+      <c r="I26" s="95"/>
+      <c r="J26" s="127" t="s">
         <v>174</v>
       </c>
-      <c r="K24" s="26"/>
-      <c r="L24" s="127" t="s">
+      <c r="K26" s="26"/>
+      <c r="L26" s="127" t="s">
         <v>177</v>
       </c>
-      <c r="M24" s="28"/>
-      <c r="N24" s="51" t="s">
+      <c r="M26" s="28"/>
+      <c r="N26" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="O24" s="161"/>
-      <c r="P24" s="60" t="s">
+      <c r="O26" s="161"/>
+      <c r="P26" s="60" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="243"/>
-      <c r="B25" s="124" t="s">
+    <row r="27" spans="1:16" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="359"/>
+      <c r="B27" s="124" t="s">
         <v>184</v>
       </c>
-      <c r="C25" s="261"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="257"/>
-      <c r="F25" s="246" t="s">
+      <c r="C27" s="361"/>
+      <c r="D27" s="106"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="354" t="s">
         <v>180</v>
       </c>
-      <c r="G25" s="257"/>
-      <c r="H25" s="253" t="s">
-        <v>254</v>
-      </c>
-      <c r="I25" s="257"/>
-      <c r="J25" s="51" t="s">
+      <c r="G27" s="356"/>
+      <c r="H27" s="350" t="s">
+        <v>261</v>
+      </c>
+      <c r="I27" s="356"/>
+      <c r="J27" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="K25" s="257"/>
-      <c r="L25" s="246" t="s">
+      <c r="K27" s="356"/>
+      <c r="L27" s="354" t="s">
         <v>182</v>
       </c>
-      <c r="M25" s="257"/>
-      <c r="N25" s="51" t="s">
+      <c r="M27" s="356"/>
+      <c r="N27" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="P25" s="92" t="s">
+      <c r="P27" s="92" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="243"/>
-      <c r="B26" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="C26" s="261"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="257"/>
-      <c r="F26" s="259"/>
-      <c r="G26" s="257"/>
-      <c r="H26" s="254"/>
-      <c r="I26" s="257"/>
-      <c r="J26" s="126" t="s">
+    <row r="28" spans="1:16" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="359"/>
+      <c r="B28" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="C28" s="361"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="345"/>
+      <c r="G28" s="356"/>
+      <c r="H28" s="351"/>
+      <c r="I28" s="356"/>
+      <c r="J28" s="126" t="s">
         <v>190</v>
       </c>
-      <c r="K26" s="257"/>
-      <c r="L26" s="259"/>
-      <c r="M26" s="257"/>
-      <c r="N26" s="51" t="s">
+      <c r="K28" s="356"/>
+      <c r="L28" s="345"/>
+      <c r="M28" s="356"/>
+      <c r="N28" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="P26" s="92" t="s">
+      <c r="P28" s="92" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:16" s="50" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="243"/>
-      <c r="B27" s="51" t="s">
+    <row r="29" spans="1:16" s="50" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="359"/>
+      <c r="B29" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="C27" s="261"/>
-      <c r="D27" s="109"/>
-      <c r="E27" s="257"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="257"/>
-      <c r="H27" s="140"/>
-      <c r="I27" s="257"/>
-      <c r="J27" s="94" t="s">
+      <c r="C29" s="361"/>
+      <c r="D29" s="109"/>
+      <c r="E29" s="356"/>
+      <c r="F29" s="137"/>
+      <c r="G29" s="356"/>
+      <c r="H29" s="140"/>
+      <c r="I29" s="356"/>
+      <c r="J29" s="94" t="s">
         <v>146</v>
       </c>
-      <c r="K27" s="257"/>
-      <c r="L27" s="126" t="s">
+      <c r="K29" s="356"/>
+      <c r="L29" s="126" t="s">
         <v>172</v>
       </c>
-      <c r="M27" s="257"/>
-      <c r="N27" s="92" t="s">
+      <c r="M29" s="356"/>
+      <c r="N29" s="92" t="s">
         <v>183</v>
       </c>
-      <c r="P27" s="170"/>
-    </row>
-    <row r="28" spans="1:16" s="50" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="244"/>
-      <c r="B28" s="51" t="s">
+      <c r="P29" s="170"/>
+    </row>
+    <row r="30" spans="1:16" s="50" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="360"/>
+      <c r="B30" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="C28" s="262"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="258"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="258"/>
-      <c r="H28" s="139"/>
-      <c r="I28" s="258"/>
-      <c r="J28" s="93" t="s">
-        <v>259</v>
-      </c>
-      <c r="K28" s="258"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="258"/>
-      <c r="N28" s="138"/>
-      <c r="O28" s="119"/>
-      <c r="P28" s="138"/>
-    </row>
-    <row r="29" spans="1:16" s="10" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="255" t="s">
-        <v>263</v>
-      </c>
-      <c r="B29" s="255"/>
-      <c r="C29" s="255"/>
-      <c r="D29" s="255"/>
-      <c r="E29" s="255"/>
-      <c r="F29" s="255"/>
-      <c r="G29" s="255"/>
-      <c r="H29" s="255"/>
-      <c r="I29" s="255"/>
-      <c r="J29" s="255"/>
-      <c r="K29" s="255"/>
-      <c r="L29" s="255"/>
-      <c r="M29" s="255"/>
-      <c r="N29" s="255"/>
-    </row>
-    <row r="30" spans="1:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-    </row>
-    <row r="31" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="78"/>
-      <c r="N31" s="78" t="s">
+      <c r="C30" s="362"/>
+      <c r="D30" s="107"/>
+      <c r="E30" s="357"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="357"/>
+      <c r="H30" s="139"/>
+      <c r="I30" s="357"/>
+      <c r="J30" s="93" t="s">
+        <v>266</v>
+      </c>
+      <c r="K30" s="357"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="357"/>
+      <c r="N30" s="138"/>
+      <c r="O30" s="119"/>
+      <c r="P30" s="138"/>
+    </row>
+    <row r="31" spans="1:16" s="10" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="335" t="s">
+        <v>270</v>
+      </c>
+      <c r="B31" s="335"/>
+      <c r="C31" s="335"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="335"/>
+      <c r="F31" s="335"/>
+      <c r="G31" s="335"/>
+      <c r="H31" s="335"/>
+      <c r="I31" s="335"/>
+      <c r="J31" s="335"/>
+      <c r="K31" s="335"/>
+      <c r="L31" s="335"/>
+      <c r="M31" s="335"/>
+      <c r="N31" s="335"/>
+    </row>
+    <row r="32" spans="1:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="78"/>
+      <c r="M33" s="78"/>
+      <c r="N33" s="78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="7"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="22" t="s">
+    <row r="34" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="7"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="68"/>
-      <c r="M32" s="78"/>
-      <c r="N32" s="68" t="s">
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="68"/>
+      <c r="M34" s="78"/>
+      <c r="N34" s="68" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G33" s="2"/>
-      <c r="H33" s="18" t="s">
+    <row r="35" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G35" s="2"/>
+      <c r="H35" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22"/>
-    </row>
-    <row r="35" spans="1:14" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-    </row>
-    <row r="36" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-    </row>
-    <row r="39" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+    </row>
+    <row r="37" spans="1:14" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="41" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -6332,44 +10839,806 @@
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
     </row>
+    <row r="42" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A29:N29"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="I25:I28"/>
-    <mergeCell ref="K25:K28"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="M25:M28"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="G25:G28"/>
-    <mergeCell ref="F21:F22"/>
+  <mergeCells count="28">
+    <mergeCell ref="F22:F23"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A11:A15"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H11:H15"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="I27:I30"/>
+    <mergeCell ref="K27:K30"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="M27:M30"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="G27:G30"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.45" right="0.2" top="0" bottom="0" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="36" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="44" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="15" max="15" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D83"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="58.5703125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="2.7109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="62.5703125" style="18" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="10" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="370" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="371"/>
+      <c r="C1" s="371"/>
+      <c r="D1" s="371"/>
+    </row>
+    <row r="2" spans="1:4" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="372" t="s">
+        <v>275</v>
+      </c>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
+      <c r="D2" s="373"/>
+    </row>
+    <row r="3" spans="1:4" s="10" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="372" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3" s="373"/>
+      <c r="C3" s="373"/>
+      <c r="D3" s="373"/>
+    </row>
+    <row r="4" spans="1:4" s="10" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="374" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="375"/>
+      <c r="C4" s="261"/>
+      <c r="D4" s="221" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="60.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="54"/>
+      <c r="D5" s="53" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="12" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="300">
+        <v>46160</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="132"/>
+      <c r="D6" s="129" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="12" customFormat="1" ht="81" x14ac:dyDescent="0.2">
+      <c r="A7" s="301"/>
+      <c r="B7" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="132"/>
+      <c r="D7" s="34" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="12" customFormat="1" ht="60.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="301"/>
+      <c r="B8" s="224" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="12" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="301"/>
+      <c r="B9" s="172" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" s="172" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="12" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="301"/>
+      <c r="B10" s="172" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" s="262"/>
+    </row>
+    <row r="11" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="198"/>
+      <c r="B11" s="199"/>
+      <c r="C11" s="200"/>
+      <c r="D11" s="201"/>
+    </row>
+    <row r="12" spans="1:4" s="12" customFormat="1" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="303">
+        <v>46161</v>
+      </c>
+      <c r="B12" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="175"/>
+      <c r="D12" s="98" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="12" customFormat="1" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="303"/>
+      <c r="B13" s="116" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="134"/>
+      <c r="D13" s="31"/>
+    </row>
+    <row r="14" spans="1:4" s="12" customFormat="1" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="303"/>
+      <c r="B14" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="C14" s="134"/>
+      <c r="D14" s="35"/>
+    </row>
+    <row r="15" spans="1:4" s="12" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="199"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="201"/>
+    </row>
+    <row r="16" spans="1:4" s="12" customFormat="1" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="303">
+        <v>46162</v>
+      </c>
+      <c r="B16" s="376" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="184"/>
+      <c r="D16" s="129" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="12" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="303"/>
+      <c r="B17" s="376"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="90" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="12" customFormat="1" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="303"/>
+      <c r="B18" s="172" t="s">
+        <v>385</v>
+      </c>
+      <c r="C18" s="63"/>
+      <c r="D18" s="172" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="12" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="303"/>
+      <c r="B19" s="172" t="s">
+        <v>382</v>
+      </c>
+      <c r="C19" s="63"/>
+      <c r="D19" s="260"/>
+    </row>
+    <row r="20" spans="1:4" s="12" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="199"/>
+      <c r="B20" s="200"/>
+      <c r="C20" s="200"/>
+      <c r="D20" s="201"/>
+    </row>
+    <row r="21" spans="1:4" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="300">
+        <v>46163</v>
+      </c>
+      <c r="B21" s="128" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="131"/>
+      <c r="D21" s="187" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="301"/>
+      <c r="B22" s="116" t="s">
+        <v>253</v>
+      </c>
+      <c r="C22" s="385"/>
+      <c r="D22" s="116" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="12" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="301"/>
+      <c r="B23" s="172" t="s">
+        <v>378</v>
+      </c>
+      <c r="C23" s="385"/>
+      <c r="D23" s="205"/>
+    </row>
+    <row r="24" spans="1:4" s="12" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="301"/>
+      <c r="B24" s="172" t="s">
+        <v>380</v>
+      </c>
+      <c r="C24" s="386"/>
+      <c r="D24" s="204"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="212"/>
+      <c r="B25" s="202"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="213"/>
+    </row>
+    <row r="26" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="301">
+        <v>46164</v>
+      </c>
+      <c r="B26" s="378" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="380" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="301"/>
+      <c r="B27" s="379"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="381"/>
+    </row>
+    <row r="28" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="301"/>
+      <c r="B28" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="33"/>
+      <c r="D28" s="172" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="301"/>
+      <c r="B29" s="172" t="s">
+        <v>381</v>
+      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="252" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="301"/>
+      <c r="B30" s="172" t="s">
+        <v>383</v>
+      </c>
+      <c r="D30" s="230"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="212"/>
+      <c r="B31" s="200"/>
+      <c r="C31" s="200"/>
+      <c r="D31" s="201"/>
+    </row>
+    <row r="32" spans="1:4" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="300">
+        <v>46165</v>
+      </c>
+      <c r="B32" s="382" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="194"/>
+      <c r="D32" s="98" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="301"/>
+      <c r="B33" s="384"/>
+      <c r="C33" s="194"/>
+      <c r="D33" s="31"/>
+    </row>
+    <row r="34" spans="1:4" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="301"/>
+      <c r="B34" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="C34" s="194"/>
+      <c r="D34" s="38"/>
+    </row>
+    <row r="35" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="206"/>
+      <c r="B35" s="200"/>
+      <c r="C35" s="200"/>
+      <c r="D35" s="201"/>
+    </row>
+    <row r="36" spans="1:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="300">
+        <v>46174</v>
+      </c>
+      <c r="B36" s="378" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" s="30"/>
+      <c r="D36" s="90" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="301"/>
+      <c r="B37" s="379"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="173"/>
+    </row>
+    <row r="38" spans="1:4" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="302"/>
+      <c r="C38" s="194"/>
+      <c r="D38" s="73"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="212"/>
+      <c r="B39" s="202"/>
+      <c r="C39" s="202"/>
+      <c r="D39" s="213"/>
+    </row>
+    <row r="40" spans="1:4" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="300">
+        <v>46175</v>
+      </c>
+      <c r="B40" s="382" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="306"/>
+      <c r="D40" s="37" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="301"/>
+      <c r="B41" s="384"/>
+      <c r="C41" s="306"/>
+      <c r="D41" s="245" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="212"/>
+      <c r="B42" s="201"/>
+      <c r="C42" s="217"/>
+      <c r="D42" s="211"/>
+    </row>
+    <row r="43" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="300">
+        <v>46176</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="C43" s="197"/>
+      <c r="D43" s="380" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="301"/>
+      <c r="C44" s="197"/>
+      <c r="D44" s="381"/>
+    </row>
+    <row r="45" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="301"/>
+      <c r="C45" s="197"/>
+      <c r="D45" s="223" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="243"/>
+      <c r="B46" s="201"/>
+      <c r="C46" s="217"/>
+      <c r="D46" s="211"/>
+    </row>
+    <row r="47" spans="1:4" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="300">
+        <v>46177</v>
+      </c>
+      <c r="B47" s="382" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="196"/>
+      <c r="D47" s="34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="301"/>
+      <c r="B48" s="383"/>
+      <c r="C48" s="197"/>
+      <c r="D48" s="34" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="301"/>
+      <c r="B49" s="384"/>
+      <c r="C49" s="197"/>
+      <c r="D49" s="172" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="301"/>
+      <c r="B50" s="263" t="s">
+        <v>206</v>
+      </c>
+      <c r="C50" s="197"/>
+      <c r="D50" s="172" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="243"/>
+      <c r="B51" s="201"/>
+      <c r="C51" s="217"/>
+      <c r="D51" s="211"/>
+    </row>
+    <row r="52" spans="1:4" ht="122.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="300">
+        <v>46178</v>
+      </c>
+      <c r="B52" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C52" s="280"/>
+      <c r="D52" s="129" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="122.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="301"/>
+      <c r="B53" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="C53" s="281"/>
+      <c r="D53" s="252" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="243"/>
+      <c r="B54" s="201"/>
+      <c r="C54" s="217"/>
+      <c r="D54" s="211"/>
+    </row>
+    <row r="55" spans="1:4" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="300">
+        <v>46179</v>
+      </c>
+      <c r="B55" s="382" t="s">
+        <v>376</v>
+      </c>
+      <c r="D55" s="90" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="301"/>
+      <c r="B56" s="384"/>
+      <c r="D56" s="266" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="301"/>
+      <c r="B57" s="176"/>
+      <c r="D57" s="223" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="243"/>
+      <c r="B58" s="230"/>
+      <c r="D58" s="224" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="243"/>
+      <c r="B59" s="201"/>
+      <c r="C59" s="217"/>
+      <c r="D59" s="211"/>
+    </row>
+    <row r="60" spans="1:4" ht="124.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="300">
+        <v>46181</v>
+      </c>
+      <c r="B60" s="223" t="s">
+        <v>197</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="124.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="301"/>
+      <c r="B61" s="382" t="s">
+        <v>311</v>
+      </c>
+      <c r="D61" s="380" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="124.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="301"/>
+      <c r="B62" s="383"/>
+      <c r="D62" s="381"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="243"/>
+      <c r="B63" s="201"/>
+      <c r="C63" s="217"/>
+      <c r="D63" s="211"/>
+    </row>
+    <row r="64" spans="1:4" ht="146.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="300">
+        <v>46182</v>
+      </c>
+      <c r="B64" s="116" t="s">
+        <v>306</v>
+      </c>
+      <c r="D64" s="90" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="146.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="301"/>
+      <c r="B65" s="116" t="s">
+        <v>305</v>
+      </c>
+      <c r="D65" s="109"/>
+    </row>
+    <row r="66" spans="1:4" ht="146.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="301"/>
+      <c r="B66" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="D66" s="109"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="198"/>
+      <c r="B67" s="201"/>
+      <c r="C67" s="217"/>
+      <c r="D67" s="211"/>
+    </row>
+    <row r="68" spans="1:4" ht="144.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="300">
+        <v>46183</v>
+      </c>
+      <c r="B68" s="223" t="s">
+        <v>308</v>
+      </c>
+      <c r="D68" s="176"/>
+    </row>
+    <row r="69" spans="1:4" ht="144.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="301"/>
+      <c r="B69" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="D69" s="167"/>
+    </row>
+    <row r="70" spans="1:4" ht="144.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="301"/>
+      <c r="B70" s="36" t="s">
+        <v>387</v>
+      </c>
+      <c r="D70" s="230"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="198"/>
+      <c r="B71" s="201"/>
+      <c r="C71" s="217"/>
+      <c r="D71" s="211"/>
+    </row>
+    <row r="72" spans="1:4" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="300">
+        <v>46184</v>
+      </c>
+      <c r="B72" s="378" t="s">
+        <v>316</v>
+      </c>
+      <c r="D72" s="34" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="301"/>
+      <c r="B73" s="379"/>
+      <c r="D73" s="167"/>
+    </row>
+    <row r="74" spans="1:4" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="301"/>
+      <c r="B74" s="36" t="s">
+        <v>388</v>
+      </c>
+      <c r="D74" s="167"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="198"/>
+      <c r="B75" s="201"/>
+      <c r="C75" s="217"/>
+      <c r="D75" s="211"/>
+    </row>
+    <row r="76" spans="1:4" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="300">
+        <v>46185</v>
+      </c>
+      <c r="B76" s="224" t="s">
+        <v>309</v>
+      </c>
+      <c r="C76" s="160"/>
+      <c r="D76" s="176"/>
+    </row>
+    <row r="77" spans="1:4" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="301"/>
+      <c r="B77" s="98" t="s">
+        <v>315</v>
+      </c>
+      <c r="D77" s="167"/>
+    </row>
+    <row r="78" spans="1:4" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="302"/>
+      <c r="B78" s="230"/>
+      <c r="C78" s="164"/>
+      <c r="D78" s="230"/>
+    </row>
+    <row r="79" spans="1:4" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="377" t="s">
+        <v>393</v>
+      </c>
+      <c r="B79" s="377"/>
+      <c r="C79" s="377"/>
+      <c r="D79" s="377"/>
+    </row>
+    <row r="82" spans="4:4" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="D82" s="68" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="D83" s="68" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="37">
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="A32:A34"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C25">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D39">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.45" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="37" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="21" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6389,53 +11658,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="264" t="s">
+      <c r="A1" s="389" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="264"/>
-      <c r="F1" s="264"/>
-      <c r="G1" s="264"/>
-      <c r="H1" s="264"/>
-      <c r="I1" s="264"/>
-      <c r="J1" s="264"/>
-      <c r="K1" s="264"/>
-      <c r="L1" s="264"/>
+      <c r="B1" s="389"/>
+      <c r="C1" s="389"/>
+      <c r="D1" s="389"/>
+      <c r="E1" s="389"/>
+      <c r="F1" s="389"/>
+      <c r="G1" s="389"/>
+      <c r="H1" s="389"/>
+      <c r="I1" s="389"/>
+      <c r="J1" s="389"/>
+      <c r="K1" s="389"/>
+      <c r="L1" s="389"/>
     </row>
     <row r="2" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="267" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" s="267"/>
-      <c r="C2" s="267"/>
-      <c r="D2" s="267"/>
-      <c r="E2" s="267"/>
-      <c r="F2" s="267"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="267"/>
-      <c r="I2" s="267"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="267"/>
-      <c r="L2" s="267"/>
+      <c r="A2" s="390" t="s">
+        <v>245</v>
+      </c>
+      <c r="B2" s="390"/>
+      <c r="C2" s="390"/>
+      <c r="D2" s="390"/>
+      <c r="E2" s="390"/>
+      <c r="F2" s="390"/>
+      <c r="G2" s="390"/>
+      <c r="H2" s="390"/>
+      <c r="I2" s="390"/>
+      <c r="J2" s="390"/>
+      <c r="K2" s="390"/>
+      <c r="L2" s="390"/>
     </row>
     <row r="3" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="263" t="s">
-        <v>267</v>
-      </c>
-      <c r="B3" s="263"/>
-      <c r="C3" s="263"/>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="263"/>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
+      <c r="A3" s="388" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3" s="388"/>
+      <c r="C3" s="388"/>
+      <c r="D3" s="388"/>
+      <c r="E3" s="388"/>
+      <c r="F3" s="388"/>
+      <c r="G3" s="388"/>
+      <c r="H3" s="388"/>
+      <c r="I3" s="388"/>
+      <c r="J3" s="388"/>
       <c r="K3" s="115"/>
       <c r="L3" s="46" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="16" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6467,18 +11736,18 @@
       </c>
     </row>
     <row r="5" spans="1:12" s="11" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="201">
-        <v>46125</v>
+      <c r="A5" s="300">
+        <v>46121</v>
       </c>
       <c r="B5" s="128" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="131"/>
-      <c r="D5" s="277" t="s">
+      <c r="D5" s="396" t="s">
         <v>197</v>
       </c>
       <c r="E5" s="29"/>
-      <c r="F5" s="274" t="s">
+      <c r="F5" s="380" t="s">
         <v>198</v>
       </c>
       <c r="G5" s="30"/>
@@ -6495,14 +11764,14 @@
       </c>
     </row>
     <row r="6" spans="1:12" s="11" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="202"/>
-      <c r="B6" s="270" t="s">
+      <c r="A6" s="301"/>
+      <c r="B6" s="382" t="s">
         <v>196</v>
       </c>
       <c r="C6" s="132"/>
-      <c r="D6" s="278"/>
+      <c r="D6" s="397"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="275"/>
+      <c r="F6" s="395"/>
       <c r="G6" s="33"/>
       <c r="H6" s="31"/>
       <c r="I6" s="35"/>
@@ -6513,12 +11782,12 @@
       </c>
     </row>
     <row r="7" spans="1:12" s="11" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="202"/>
-      <c r="B7" s="271"/>
+      <c r="A7" s="301"/>
+      <c r="B7" s="384"/>
       <c r="C7" s="133"/>
       <c r="D7" s="130"/>
       <c r="E7" s="32"/>
-      <c r="F7" s="276"/>
+      <c r="F7" s="381"/>
       <c r="G7" s="33"/>
       <c r="H7" s="35"/>
       <c r="I7" s="35"/>
@@ -6529,7 +11798,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" s="11" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="203"/>
+      <c r="A8" s="302"/>
       <c r="B8" s="36" t="s">
         <v>213</v>
       </c>
@@ -6543,7 +11812,7 @@
       <c r="J8" s="73"/>
       <c r="K8" s="183"/>
       <c r="L8" s="116" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="11" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6561,22 +11830,24 @@
       <c r="L9" s="178"/>
     </row>
     <row r="10" spans="1:12" s="11" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="201">
-        <v>46126</v>
+      <c r="A10" s="300">
+        <v>46122</v>
       </c>
       <c r="B10" s="128" t="s">
         <v>115</v>
       </c>
       <c r="C10" s="175"/>
-      <c r="D10" s="279" t="s">
+      <c r="D10" s="398" t="s">
         <v>205</v>
       </c>
       <c r="E10" s="29"/>
-      <c r="F10" s="270" t="s">
+      <c r="F10" s="382" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="29"/>
-      <c r="H10" s="194"/>
+      <c r="H10" s="313" t="s">
+        <v>240</v>
+      </c>
       <c r="I10" s="31"/>
       <c r="J10" s="37" t="s">
         <v>207</v>
@@ -6587,16 +11858,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" s="11" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="202"/>
+      <c r="A11" s="301"/>
       <c r="B11" s="128" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C11" s="134"/>
-      <c r="D11" s="280"/>
+      <c r="D11" s="399"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="271"/>
+      <c r="F11" s="384"/>
       <c r="G11" s="32"/>
-      <c r="H11" s="195"/>
+      <c r="H11" s="314"/>
       <c r="I11" s="35"/>
       <c r="J11" s="37" t="s">
         <v>210</v>
@@ -6607,7 +11878,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" s="11" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="202"/>
+      <c r="A12" s="301"/>
       <c r="B12" s="34" t="s">
         <v>211</v>
       </c>
@@ -6616,28 +11887,28 @@
       <c r="E12" s="32"/>
       <c r="F12" s="173"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="195"/>
+      <c r="H12" s="314"/>
       <c r="I12" s="35"/>
       <c r="J12" s="173"/>
       <c r="K12" s="58"/>
       <c r="L12" s="172" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="11" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="203"/>
+      <c r="A13" s="302"/>
       <c r="B13" s="41"/>
       <c r="C13" s="134"/>
       <c r="D13" s="38"/>
       <c r="E13" s="32"/>
       <c r="F13" s="73"/>
       <c r="G13" s="32"/>
-      <c r="H13" s="196"/>
+      <c r="H13" s="369"/>
       <c r="I13" s="35"/>
       <c r="J13" s="73"/>
       <c r="K13" s="59"/>
       <c r="L13" s="172" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6655,22 +11926,22 @@
       <c r="L14" s="44"/>
     </row>
     <row r="15" spans="1:12" s="11" customFormat="1" ht="133.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="201">
-        <v>46127</v>
-      </c>
-      <c r="B15" s="265" t="s">
+      <c r="A15" s="300">
+        <v>46123</v>
+      </c>
+      <c r="B15" s="378" t="s">
         <v>214</v>
       </c>
       <c r="C15" s="184"/>
-      <c r="D15" s="270" t="s">
+      <c r="D15" s="382" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="29"/>
-      <c r="F15" s="268" t="s">
+      <c r="F15" s="391" t="s">
         <v>209</v>
       </c>
       <c r="G15" s="30"/>
-      <c r="H15" s="272" t="s">
+      <c r="H15" s="393" t="s">
         <v>216</v>
       </c>
       <c r="I15" s="31"/>
@@ -6683,14 +11954,14 @@
       </c>
     </row>
     <row r="16" spans="1:12" s="11" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="202"/>
-      <c r="B16" s="266"/>
+      <c r="A16" s="301"/>
+      <c r="B16" s="379"/>
       <c r="C16" s="59"/>
-      <c r="D16" s="271"/>
+      <c r="D16" s="384"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="269"/>
+      <c r="F16" s="392"/>
       <c r="G16" s="33"/>
-      <c r="H16" s="273"/>
+      <c r="H16" s="394"/>
       <c r="I16" s="35"/>
       <c r="K16" s="35"/>
       <c r="L16" s="187" t="s">
@@ -6698,7 +11969,7 @@
       </c>
     </row>
     <row r="17" spans="1:12" s="11" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="202"/>
+      <c r="A17" s="301"/>
       <c r="B17" s="31"/>
       <c r="C17" s="59"/>
       <c r="D17" s="173"/>
@@ -6709,11 +11980,11 @@
       <c r="I17" s="35"/>
       <c r="K17" s="35"/>
       <c r="L17" s="172" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="11" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="203"/>
+      <c r="A18" s="302"/>
       <c r="B18" s="38"/>
       <c r="C18" s="185"/>
       <c r="D18" s="73"/>
@@ -6724,7 +11995,7 @@
       <c r="I18" s="35"/>
       <c r="K18" s="35"/>
       <c r="L18" s="172" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6742,14 +12013,14 @@
       <c r="L19" s="44"/>
     </row>
     <row r="20" spans="1:12" s="11" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="201">
-        <v>46128</v>
-      </c>
-      <c r="B20" s="265" t="s">
+      <c r="A20" s="300">
+        <v>46125</v>
+      </c>
+      <c r="B20" s="378" t="s">
         <v>203</v>
       </c>
       <c r="C20" s="131"/>
-      <c r="D20" s="270" t="s">
+      <c r="D20" s="382" t="s">
         <v>116</v>
       </c>
       <c r="E20" s="29"/>
@@ -6757,7 +12028,7 @@
         <v>218</v>
       </c>
       <c r="G20" s="30"/>
-      <c r="H20" s="268" t="s">
+      <c r="H20" s="391" t="s">
         <v>206</v>
       </c>
       <c r="I20" s="31"/>
@@ -6768,16 +12039,16 @@
       </c>
     </row>
     <row r="21" spans="1:12" s="11" customFormat="1" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="202"/>
-      <c r="B21" s="266"/>
+      <c r="A21" s="301"/>
+      <c r="B21" s="379"/>
       <c r="C21" s="135"/>
-      <c r="D21" s="271"/>
+      <c r="D21" s="384"/>
       <c r="E21" s="32"/>
       <c r="F21" s="34" t="s">
         <v>221</v>
       </c>
       <c r="G21" s="33"/>
-      <c r="H21" s="269"/>
+      <c r="H21" s="392"/>
       <c r="I21" s="35"/>
       <c r="J21" s="174"/>
       <c r="K21" s="35"/>
@@ -6786,7 +12057,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" s="11" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="202"/>
+      <c r="A22" s="301"/>
       <c r="B22" s="90" t="s">
         <v>215</v>
       </c>
@@ -6806,7 +12077,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" s="11" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="203"/>
+      <c r="A23" s="302"/>
       <c r="B23" s="136"/>
       <c r="D23" s="38"/>
       <c r="E23" s="74"/>
@@ -6819,20 +12090,20 @@
       <c r="L23" s="73"/>
     </row>
     <row r="24" spans="1:12" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="281" t="s">
-        <v>263</v>
-      </c>
-      <c r="B24" s="281"/>
-      <c r="C24" s="281"/>
-      <c r="D24" s="281"/>
-      <c r="E24" s="281"/>
-      <c r="F24" s="281"/>
-      <c r="G24" s="281"/>
-      <c r="H24" s="281"/>
-      <c r="I24" s="281"/>
-      <c r="J24" s="281"/>
-      <c r="K24" s="281"/>
-      <c r="L24" s="281"/>
+      <c r="A24" s="387" t="s">
+        <v>270</v>
+      </c>
+      <c r="B24" s="387"/>
+      <c r="C24" s="387"/>
+      <c r="D24" s="387"/>
+      <c r="E24" s="387"/>
+      <c r="F24" s="387"/>
+      <c r="G24" s="387"/>
+      <c r="H24" s="387"/>
+      <c r="I24" s="387"/>
+      <c r="J24" s="387"/>
+      <c r="K24" s="387"/>
+      <c r="L24" s="387"/>
     </row>
     <row r="25" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="17"/>
@@ -6878,12 +12149,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A10:A13"/>
+  <mergeCells count="21">
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B20:B21"/>
@@ -6899,6 +12165,12 @@
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="H10:H13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.45" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
